--- a/docs/qa/web-qa-sheet.xlsx
+++ b/docs/qa/web-qa-sheet.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'TC 시나리오'!$A$1:$R$132</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'요청사항(REQ)'!$A$1:$U$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'요청사항(REQ)'!$A$1:$U$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -560,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -851,31 +851,31 @@
     </row>
     <row r="18">
       <c r="A18" s="7">
-        <f>COUNTA('요청사항(REQ)'!A2:A9)</f>
+        <f>COUNTA('요청사항(REQ)'!A2:A10)</f>
         <v/>
       </c>
       <c r="B18" s="7">
-        <f>COUNTIF('요청사항(REQ)'!Q2:Q9,"확인 전")</f>
+        <f>COUNTIF('요청사항(REQ)'!Q2:Q10,"확인 전")</f>
         <v/>
       </c>
       <c r="C18" s="7">
-        <f>COUNTIF('요청사항(REQ)'!Q2:Q9,"처리 중")</f>
+        <f>COUNTIF('요청사항(REQ)'!Q2:Q10,"처리 중")</f>
         <v/>
       </c>
       <c r="D18" s="7">
-        <f>COUNTIF('요청사항(REQ)'!Q2:Q9,"처리 완료")</f>
+        <f>COUNTIF('요청사항(REQ)'!Q2:Q10,"처리 완료")</f>
         <v/>
       </c>
       <c r="E18" s="7">
-        <f>COUNTIF('요청사항(REQ)'!S2:S9,"검수 완료")</f>
+        <f>COUNTIF('요청사항(REQ)'!S2:S10,"검수 완료")</f>
         <v/>
       </c>
       <c r="F18" s="7">
-        <f>COUNTIF('요청사항(REQ)'!C2:C9,"긴급 버그")</f>
+        <f>COUNTIF('요청사항(REQ)'!C2:C10,"긴급 버그")</f>
         <v/>
       </c>
       <c r="G18" s="7">
-        <f>COUNTIF('요청사항(REQ)'!D2:D9,"Critical")</f>
+        <f>COUNTIF('요청사항(REQ)'!D2:D10,"Critical")</f>
         <v/>
       </c>
     </row>
@@ -1237,36 +1237,43 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>- 로컬에 OACX 설정이 없어 모바일 신분증 발급 요청 구간은 프로덕션에서만 확인된다(TC-Y07 이후 구간).</t>
+          <t>- 배포가 세션 중에 바뀌면 같은 TC 가 다른 코드를 본다. 라운드마다 배포 커밋을 적어 두는 편이 낫다.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>- 코드 레벨 원인 — REQ 의 '해결 방향'은 가설과 실제 수정 내용을 함께 적었고, 검수는 별도다.</t>
+          <t>- 로컬에 OACX 설정이 없어 모바일 신분증 발급 요청 구간은 프로덕션에서만 확인된다(TC-Y07 이후 구간).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
+          <t>- 코드 레벨 원인 — REQ 의 '해결 방향'은 가설과 실제 수정 내용을 함께 적었고, 검수는 별도다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
           <t>- 명세 17.3 게이트(증권성 법률의견·신탁사 계약·은행/PG/모바일 신분증 실계약)는 개발 범위 밖이다</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="10" t="inlineStr"/>
-    </row>
     <row r="56">
-      <c r="A56" s="11" t="inlineStr">
+      <c r="A56" s="10" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t>출시 가능 여부는 이 시트가 판정하지 않습니다. 결정은 만든 사람이 합니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="46">
     <mergeCell ref="A48:H48"/>
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="B9:H9"/>
@@ -1292,6 +1299,7 @@
     <mergeCell ref="A50:H50"/>
     <mergeCell ref="A56:H56"/>
     <mergeCell ref="A55:H55"/>
+    <mergeCell ref="A57:H57"/>
     <mergeCell ref="A42:H42"/>
     <mergeCell ref="C27:G27"/>
     <mergeCell ref="B2:H2"/>
@@ -11862,7 +11870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12701,7 +12709,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>기능 결함</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -12716,17 +12724,17 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>프로덕션에서 데모 리셋을 돌려도 시연 계정(demo@farmfi.test)이 만들어지지 않는다</t>
+          <t>데모 리셋이 시드 계정뿐 아니라 실제 가입 계정까지 지운다</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>seedScenario가 '시연' 투자자를 생성하므로 리셋 후 demo@farmfi.test 로 로그인할 수 있어야 한다.</t>
+          <t>리셋은 시연 데이터를 최초 상태로 되돌리는 동작이다. 실제로 가입한 계정과 그 계정의 본인확인 기록은 남아야 한다.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>POST /api/demo/reset 두 번 모두 응답의 investors 가 [김투자, 이서연, 박준혁]이고 DB에도 시연 계정이 없다. 로그인 401. 코드(HEAD·origin/main 모두)에는 생성 블록이 있다.</t>
+          <t>seedScenario 가 재생성 전에 prisma.user.deleteMany() 로 유저 테이블을 통째로 비운다(seed-scenario.ts:84). 리셋 한 번에 tj041600@naver.com 계정과 거기 붙은 OpenDID 검증 기록 5건이 사라진다. QA 중에는 매 리셋마다 백업했다가 복원해서 이어갔다.</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -12756,12 +12764,12 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>리셋 응답 {"status":"reset","investors":["김투자","이서연","박준혁"]} · User 테이블 조회 결과</t>
+          <t>seed-scenario.ts:84 · 리셋 전후 User 테이블 조회 (실계정 소멸 → 수동 복원)</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>원인 가설: 배포본이 origin/main 보다 오래된 커밋일 수 있다. 확인할 것 — Vercel 최신 배포의 커밋 SHA와 origin/main(c8675cf0) 대조. 발표 전에 확인이 필요하다(시연 계정으로 본인확인 흐름을 보여주는 구성이라면 리셋 직후 로그인이 안 된다). QA 중에는 시드 정의대로 계정을 직접 만들어 이어서 검증했다.</t>
+          <t>원인 가설: 시드가 멱등하려면 지우고 다시 만드는 게 가장 단순해서 전체 삭제로 짰다. 확인할 것 — 시드 계정만 지울지(`@farmfi.test` 로 한정), 아니면 리셋 범위에서 User 를 빼고 시연 데이터만 되돌릴지. 발표 전 리셋을 한 번이라도 돌릴 계획이면 결정이 필요하다.</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr"/>
@@ -12779,25 +12787,116 @@
       <c r="T9" s="3" t="inlineStr"/>
       <c r="U9" s="3" t="inlineStr"/>
     </row>
+    <row r="10" ht="88" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>REQ-009</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>3순위</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>리셋 직후 시연 계정(demo@farmfi.test)이 만들어지지 않은 적이 있다 — 재현 안 됨</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>리셋을 돌리면 seedScenario 가 '시연' 투자자를 만들고 그 계정으로 로그인할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>리셋 두 번 연속으로 응답의 investors 가 [김투자, 이서연, 박준혁] 이고 DB 에도 시연 계정이 없었다. 로그인 401. 같은 세션 뒤쪽에서 다시 리셋하니 시드 순번 그대로 정상 생성됐다(id cmt7kzoxr…, 최영호와 김투자 사이).</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>관리자 &gt; 데모 리셋</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>1회</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>리셋 응답 · User 테이블 조회 2회(없음) → 이후 조회(있음, 시드 순번 id)</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>원인 가설: 관측 사이에 앱 쪽 커밋이 올라와 재배포됐다. 앞선 두 번은 시연 계정 생성 블록이 없는 배포본이었을 수 있다. 확인할 것 — 다음 라운드에서 배포 커밋 SHA 를 적고 리셋을 한 번 더 돌려 본다. 재현되지 않으면 닫는다. 별도 세션을 잡을 일은 아니고 다음 QA 라운드에 얹으면 된다.</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>확인 전</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t>검수 전</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U9"/>
+  <autoFilter ref="A1:U10"/>
   <dataValidations count="6">
-    <dataValidation sqref="C2:C9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"긴급 버그,기능 결함,UX,UI 개선,콘텐츠·문구,성능,기타"</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Critical,Major,Minor"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1순위,2순위,3순위"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"항상,가끔,1회"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q2:Q10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"확인 전,처리 중,처리 완료,검수 완료,보류"</formula1>
     </dataValidation>
-    <dataValidation sqref="S2:S9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="S2:S10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"검수 전,검수 완료,반려"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/qa/web-qa-sheet.xlsx
+++ b/docs/qa/web-qa-sheet.xlsx
@@ -12815,7 +12815,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>리셋 직후 시연 계정(demo@farmfi.test)이 만들어지지 않은 적이 있다 — 재현 안 됨</t>
+          <t>리셋 직후 시연 계정(demo@farmfi.test)이 만들어지지 않았다 — 결함 아님, 원인 확인</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -12855,18 +12855,22 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>리셋 응답 · User 테이블 조회 2회(없음) → 이후 조회(있음, 시드 순번 id)</t>
+          <t>리셋 응답 · User 테이블 조회 2회(없음) → 이후 조회(있음, 시드 순번 id cmt7kzoxr…) · 커밋 5ed2c88c 와 그 배포 시각</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>원인 가설: 관측 사이에 앱 쪽 커밋이 올라와 재배포됐다. 앞선 두 번은 시연 계정 생성 블록이 없는 배포본이었을 수 있다. 확인할 것 — 다음 라운드에서 배포 커밋 SHA 를 적고 리셋을 한 번 더 돌려 본다. 재현되지 않으면 닫는다. 별도 세션을 잡을 일은 아니고 다음 QA 라운드에 얹으면 된다.</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t>확인 전</t>
+          <t>결함이 아니다. 커밋 5ed2c88c `feat: 초기화해도 시연 계정이 살아남게 한다`(08-24 22:07)가 시드에 시연 계정 생성 블록을 넣었고, 그 배포가 내 관측 두 번 사이에 들어갔다. 앞선 두 번은 그 블록이 없는 배포본이었다. 남기는 이유는 하나다 — QA 중에 다른 세션이 같은 저장소에 배포하면 같은 TC 가 다른 코드를 본다. 라운드마다 배포 커밋 SHA 를 적는다.</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="Q10" s="13" t="inlineStr">
+        <is>
+          <t>처리 완료</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr"/>
@@ -12875,7 +12879,11 @@
           <t>검수 전</t>
         </is>
       </c>
-      <c r="T10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
       <c r="U10" s="3" t="inlineStr"/>
     </row>
   </sheetData>

--- a/docs/qa/web-qa-sheet.xlsx
+++ b/docs/qa/web-qa-sheet.xlsx
@@ -1090,7 +1090,7 @@
       <c r="G28" s="5" t="n"/>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>58개 화면 본문 정규식 검사 0건. ※ 요청 3으로 '총 배정 토큰·내 보유 토큰' 라벨이 추가돼 다음 라운드에서 이 기준을 다시 본다</t>
+          <t>58개 화면 본문 정규식 검사 0건. 이후 I-01 배분 현황 카드에 '총 배정 토큰·내 보유 토큰' 라벨이 들어갔고, 명세 18장이 그 두 개를 예외로 명시하도록 갱신됐다(값은 구좌로 센다)</t>
         </is>
       </c>
     </row>

--- a/docs/qa/web-qa-sheet.xlsx
+++ b/docs/qa/web-qa-sheet.xlsx
@@ -165,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -193,6 +193,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -588,7 +592,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>https://farmfi.co.kr (프로덕션) · 재검증은 같은 코드의 로컬 dev</t>
+          <t>https://farmfi.co.kr (프로덕션)</t>
         </is>
       </c>
       <c r="C2" s="4" t="n"/>
@@ -624,7 +628,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>1차 = 수정 전 프로덕션 QA · 2차 = 수정 반영 후 재검증 + 추가 요청 확인</t>
+          <t>1차 = 수정 전 프로덕션 QA · 2차 = 수정 반영 후 로컬 dev 재검증 + 추가 요청 확인 · 3차 = 같은 TC 를 배포본에서 재실행</t>
         </is>
       </c>
       <c r="C4" s="4" t="n"/>
@@ -696,7 +700,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>1차 2026-08-25 · 2차 2026-08-25</t>
+          <t>1차 2026-08-25 · 2차 2026-08-25 · 3차 2026-08-26</t>
         </is>
       </c>
       <c r="C8" s="4" t="n"/>
@@ -724,6 +728,18 @@
       <c r="G9" s="4" t="n"/>
       <c r="H9" s="5" t="n"/>
     </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>배포 커밋</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>1차 752175f5~5ed2c88c(세션 중 재배포) · 2차 로컬 dev · 3차 e81d8a05</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -770,27 +786,27 @@
     </row>
     <row r="13">
       <c r="A13" s="7">
-        <f>COUNTA('TC 시나리오'!B2:B132)</f>
+        <f>COUNTA('TC 시나리오'!B2:B168)</f>
         <v/>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF('TC 시나리오'!M2:M132,"Pass")</f>
+        <f>COUNTIF('TC 시나리오'!M2:M168,"Pass")</f>
         <v/>
       </c>
       <c r="C13" s="7">
-        <f>COUNTIF('TC 시나리오'!M2:M132,"Fail")</f>
+        <f>COUNTIF('TC 시나리오'!M2:M168,"Fail")</f>
         <v/>
       </c>
       <c r="D13" s="7">
-        <f>COUNTIF('TC 시나리오'!M2:M132,"Blocked")</f>
+        <f>COUNTIF('TC 시나리오'!M2:M168,"Blocked")</f>
         <v/>
       </c>
       <c r="E13" s="7">
-        <f>COUNTIF('TC 시나리오'!M2:M132,"N/A")</f>
+        <f>COUNTIF('TC 시나리오'!M2:M168,"N/A")</f>
         <v/>
       </c>
       <c r="F13" s="7">
-        <f>COUNTIF('TC 시나리오'!M2:M132,"미실행")</f>
+        <f>COUNTIF('TC 시나리오'!M2:M168,"미실행")</f>
         <v/>
       </c>
       <c r="G13" s="7">
@@ -801,7 +817,7 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>1차 Fail 12건은 모두 수정 후 2차에서 Pass로 재확인됐다. 2차 TC는 별도 코드(TC-X·TC-Y)로 남겨 1차 판정을 덮어쓰지 않는다.</t>
+          <t>1차 Fail 12건은 수정 후 2차에서 Pass로 재확인됐고, 3차에서 배포본으로 같은 TC 를 다시 확인했다. 라운드마다 행을 새로 쌓아 앞 라운드 판정을 덮어쓰지 않는다.</t>
         </is>
       </c>
     </row>
@@ -998,7 +1014,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>TC-O01, TC-X14</t>
+          <t>TC-O01, TC-X14, TC-X15</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -1012,7 +1028,7 @@
       <c r="G25" s="5" t="n"/>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>1차에서 operatorId 미지정 지점이 통과(REQ-003) → 수정 후 403 확인</t>
+          <t>1차에서 operatorId 미지정 지점이 통과(REQ-003) → 수정 후 미배정·타인 배정 모두 403. 3차에서 배포본 재확인</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1092,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>TC-W01</t>
+          <t>TC-W01, TC-W02</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -1090,7 +1106,7 @@
       <c r="G28" s="5" t="n"/>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>58개 화면 본문 정규식 검사 0건. 이후 I-01 배분 현황 카드에 '총 배정 토큰·내 보유 토큰' 라벨이 들어갔고, 명세 18장이 그 두 개를 예외로 명시하도록 갱신됐다(값은 구좌로 센다)</t>
+          <t>1차 58개 화면 정규식 검사 0건. 이후 I-01 배분 현황 카드에 '총 배정 토큰·내 보유 토큰' 라벨이 들어갔고, 명세 18장이 그 두 개를 예외로 명시하도록 갱신됐다(값은 구좌로 센다). 3차 재검사 0건</t>
         </is>
       </c>
     </row>
@@ -1223,30 +1239,26 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>- 실제 은행 송금·PG 결제·모바일 신분증 발급기관 응답 (Mock·시드 계정 기준으로 검증)</t>
+          <t>- 실제 은행 송금·PG 결제는 지급사 웹훅 규약대로 호출하되 입금 자체는 시뮬레이션이다. 모바일 신분증은 3차에서 발급 요청까지 확인했다(TC-Z01).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>- 2차 재검증은 로컬 dev 에서 했다. 배포 후 프로덕션에서 같은 TC 를 한 번 더 돌려야 한다.</t>
+          <t>- 3차는 배포본 e81d8a05 기준이다. 그 뒤 배포가 있으면 같은 TC 가 다른 코드를 본다.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>- 배포가 세션 중에 바뀌면 같은 TC 가 다른 코드를 본다. 라운드마다 배포 커밋을 적어 두는 편이 낫다.</t>
+          <t>- 라운드마다 배포 커밋을 적는다. 1차 QA 중 세션 도중 재배포가 실제로 있었다(REQ-009).</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>- 로컬에 OACX 설정이 없어 모바일 신분증 발급 요청 구간은 프로덕션에서만 확인된다(TC-Y07 이후 구간).</t>
-        </is>
-      </c>
+      <c r="A53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
@@ -1331,7 +1343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R132"/>
+  <dimension ref="A1:R168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11844,19 +11856,3119 @@
         </is>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>TC-X01</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>F-13</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>/api/optimization/[id]</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>비회원이 생육 최적화 API 조회</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>API/브라우저로 직접 실행</t>
+        </is>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="n"/>
+      <c r="L133" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M133" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O133" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P133" s="3" t="inlineStr">
+        <is>
+          <t>REQ-005</t>
+        </is>
+      </c>
+      <c r="Q133" s="3" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="R133" s="3" t="inlineStr">
+        <is>
+          <t>1순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>TC-X02</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>F-13</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>/api/briefing/[id]</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>비회원이 브리핑 API 조회</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I134" s="3" t="inlineStr">
+        <is>
+          <t>API/브라우저로 직접 실행</t>
+        </is>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="n"/>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M134" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O134" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P134" s="3" t="inlineStr">
+        <is>
+          <t>REQ-005</t>
+        </is>
+      </c>
+      <c r="Q134" s="3" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="R134" s="3" t="inlineStr">
+        <is>
+          <t>1순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="n">
+        <v>135</v>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>TC-X03</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>F-13</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>/api/optimization/[id]</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>투자자가 남의 지점 최적화 API 조회</t>
+        </is>
+      </c>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I135" s="3" t="inlineStr">
+        <is>
+          <t>API/브라우저로 직접 실행</t>
+        </is>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>403 배정되지 않은 매장</t>
+        </is>
+      </c>
+      <c r="K135" s="3" t="n"/>
+      <c r="L135" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M135" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O135" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P135" s="3" t="inlineStr">
+        <is>
+          <t>REQ-005</t>
+        </is>
+      </c>
+      <c r="Q135" s="3" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="R135" s="3" t="inlineStr">
+        <is>
+          <t>1순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="n">
+        <v>136</v>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>TC-X04</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>F-13</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>/api/optimization/[id]</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>배정 운영자가 최적화 API 조회 (정상 경로 유지)</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I136" s="3" t="inlineStr">
+        <is>
+          <t>API/브라우저로 직접 실행</t>
+        </is>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="K136" s="3" t="n"/>
+      <c r="L136" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M136" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O136" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P136" s="3" t="inlineStr">
+        <is>
+          <t>REQ-005</t>
+        </is>
+      </c>
+      <c r="Q136" s="3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="R136" s="3" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="n">
+        <v>137</v>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>TC-X05</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>F-13</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>/optimization/[id]</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>비회원이 최적화 화면 진입</t>
+        </is>
+      </c>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t>API/브라우저로 직접 실행</t>
+        </is>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t>/login 으로 이동</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="n"/>
+      <c r="L137" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M137" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O137" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P137" s="3" t="inlineStr">
+        <is>
+          <t>REQ-005</t>
+        </is>
+      </c>
+      <c r="Q137" s="3" t="inlineStr">
+        <is>
+          <t>/login?next=/operator</t>
+        </is>
+      </c>
+      <c r="R137" s="3" t="inlineStr">
+        <is>
+          <t>1순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>TC-X06</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>F-13</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>/optimization/[id]</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>투자자가 최적화 화면 진입</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I138" s="3" t="inlineStr">
+        <is>
+          <t>API/브라우저로 직접 실행</t>
+        </is>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>자기 역할 홈으로 이동</t>
+        </is>
+      </c>
+      <c r="K138" s="3" t="n"/>
+      <c r="L138" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M138" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O138" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P138" s="3" t="inlineStr">
+        <is>
+          <t>REQ-005</t>
+        </is>
+      </c>
+      <c r="Q138" s="3" t="inlineStr">
+        <is>
+          <t>/investor</t>
+        </is>
+      </c>
+      <c r="R138" s="3" t="inlineStr">
+        <is>
+          <t>1순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="n">
+        <v>139</v>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>TC-X07</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>F-17</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>/admin</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>투자자 세션으로 /admin 진입</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I139" s="3" t="inlineStr">
+        <is>
+          <t>API/브라우저로 직접 실행</t>
+        </is>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>/investor 로 리다이렉트</t>
+        </is>
+      </c>
+      <c r="K139" s="3" t="n"/>
+      <c r="L139" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M139" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O139" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P139" s="3" t="inlineStr">
+        <is>
+          <t>REQ-004</t>
+        </is>
+      </c>
+      <c r="Q139" s="3" t="inlineStr">
+        <is>
+          <t>/investor</t>
+        </is>
+      </c>
+      <c r="R139" s="3" t="inlineStr">
+        <is>
+          <t>1순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>TC-X08</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>F-17</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>/admin/ledger</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>투자자 세션으로 /admin/ledger 진입</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I140" s="3" t="inlineStr">
+        <is>
+          <t>API/브라우저로 직접 실행</t>
+        </is>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>/investor 로 리다이렉트</t>
+        </is>
+      </c>
+      <c r="K140" s="3" t="n"/>
+      <c r="L140" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M140" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O140" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P140" s="3" t="inlineStr">
+        <is>
+          <t>REQ-004</t>
+        </is>
+      </c>
+      <c r="Q140" s="3" t="inlineStr">
+        <is>
+          <t>/investor</t>
+        </is>
+      </c>
+      <c r="R140" s="3" t="inlineStr">
+        <is>
+          <t>1순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="n">
+        <v>141</v>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>TC-X09</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>F-17</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>/operator/milestones</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>투자자 세션으로 운영자 화면 진입</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I141" s="3" t="inlineStr">
+        <is>
+          <t>API/브라우저로 직접 실행</t>
+        </is>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>/investor 로 리다이렉트</t>
+        </is>
+      </c>
+      <c r="K141" s="3" t="n"/>
+      <c r="L141" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M141" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O141" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P141" s="3" t="inlineStr">
+        <is>
+          <t>REQ-004</t>
+        </is>
+      </c>
+      <c r="Q141" s="3" t="inlineStr">
+        <is>
+          <t>/investor</t>
+        </is>
+      </c>
+      <c r="R141" s="3" t="inlineStr">
+        <is>
+          <t>1순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="n">
+        <v>142</v>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>TC-X10</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>F-17</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>/landlord</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>투자자 세션으로 임대인 화면 진입</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I142" s="3" t="inlineStr">
+        <is>
+          <t>API/브라우저로 직접 실행</t>
+        </is>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>/investor 로 리다이렉트</t>
+        </is>
+      </c>
+      <c r="K142" s="3" t="n"/>
+      <c r="L142" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M142" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O142" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P142" s="3" t="inlineStr">
+        <is>
+          <t>REQ-004</t>
+        </is>
+      </c>
+      <c r="Q142" s="3" t="inlineStr">
+        <is>
+          <t>/investor</t>
+        </is>
+      </c>
+      <c r="R142" s="3" t="inlineStr">
+        <is>
+          <t>1순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>TC-X11</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>F-14</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>/admin</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>관리자가 /admin 진입 (정상 경로 유지)</t>
+        </is>
+      </c>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I143" s="3" t="inlineStr">
+        <is>
+          <t>API/브라우저로 직접 실행</t>
+        </is>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>그대로 열림</t>
+        </is>
+      </c>
+      <c r="K143" s="3" t="n"/>
+      <c r="L143" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M143" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O143" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P143" s="3" t="inlineStr">
+        <is>
+          <t>REQ-004</t>
+        </is>
+      </c>
+      <c r="Q143" s="3" t="inlineStr">
+        <is>
+          <t>/admin</t>
+        </is>
+      </c>
+      <c r="R143" s="3" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>TC-X12</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>F-11</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>/operator/milestones</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="inlineStr">
+        <is>
+          <t>운영자가 운영자 화면 진입 (정상 경로 유지)</t>
+        </is>
+      </c>
+      <c r="H144" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I144" s="3" t="inlineStr">
+        <is>
+          <t>API/브라우저로 직접 실행</t>
+        </is>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>그대로 열림</t>
+        </is>
+      </c>
+      <c r="K144" s="3" t="n"/>
+      <c r="L144" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M144" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O144" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P144" s="3" t="inlineStr">
+        <is>
+          <t>REQ-004</t>
+        </is>
+      </c>
+      <c r="Q144" s="3" t="inlineStr">
+        <is>
+          <t>/operator/milestones</t>
+        </is>
+      </c>
+      <c r="R144" s="3" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>TC-X13</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>F-06</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>/api/subscribe</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>우회 라우트 직접 호출</t>
+        </is>
+      </c>
+      <c r="H145" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I145" s="3" t="inlineStr">
+        <is>
+          <t>API/브라우저로 직접 실행</t>
+        </is>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>404 (라우트 없음)</t>
+        </is>
+      </c>
+      <c r="K145" s="3" t="n"/>
+      <c r="L145" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M145" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O145" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P145" s="3" t="inlineStr">
+        <is>
+          <t>REQ-002</t>
+        </is>
+      </c>
+      <c r="Q145" s="3" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="R145" s="3" t="inlineStr">
+        <is>
+          <t>1순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="n">
+        <v>146</v>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>TC-X14</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>F-12</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>O-11</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="inlineStr">
+        <is>
+          <t>미배정 지점(operatorId 없음)에 증빙 제출</t>
+        </is>
+      </c>
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I146" s="3" t="inlineStr">
+        <is>
+          <t>API/브라우저로 직접 실행</t>
+        </is>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="K146" s="3" t="n"/>
+      <c r="L146" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M146" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O146" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P146" s="3" t="inlineStr">
+        <is>
+          <t>REQ-003</t>
+        </is>
+      </c>
+      <c r="Q146" s="3" t="inlineStr">
+        <is>
+          <t>403 배정된 지점의 운영자만 제출할 수 있습니다</t>
+        </is>
+      </c>
+      <c r="R146" s="3" t="inlineStr">
+        <is>
+          <t>1순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="n">
+        <v>147</v>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>TC-X15</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>F-12</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>O-11</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>남의 배정 지점에 증빙 제출</t>
+        </is>
+      </c>
+      <c r="H147" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I147" s="3" t="inlineStr">
+        <is>
+          <t>API/브라우저로 직접 실행</t>
+        </is>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="K147" s="3" t="n"/>
+      <c r="L147" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M147" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O147" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P147" s="3" t="inlineStr">
+        <is>
+          <t>REQ-003</t>
+        </is>
+      </c>
+      <c r="Q147" s="3" t="inlineStr">
+        <is>
+          <t>403 배정된 지점의 운영자만 제출할 수 있습니다</t>
+        </is>
+      </c>
+      <c r="R147" s="3" t="inlineStr">
+        <is>
+          <t>1순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="n">
+        <v>148</v>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>TC-X16</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>F-12</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>O-11</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>배정 운영자 증빙 제출 (정상 경로 유지)</t>
+        </is>
+      </c>
+      <c r="H148" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I148" s="3" t="inlineStr">
+        <is>
+          <t>API/브라우저로 직접 실행</t>
+        </is>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>200 · evidence_submitted</t>
+        </is>
+      </c>
+      <c r="K148" s="3" t="n"/>
+      <c r="L148" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M148" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O148" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P148" s="3" t="inlineStr">
+        <is>
+          <t>REQ-003</t>
+        </is>
+      </c>
+      <c r="Q148" s="3" t="inlineStr">
+        <is>
+          <t>200 · evidence_submitted</t>
+        </is>
+      </c>
+      <c r="R148" s="3" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="n">
+        <v>149</v>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>TC-X17</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>F-07</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>1차 입금 웹훅 (정상 경로 유지)</t>
+        </is>
+      </c>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I149" s="3" t="inlineStr">
+        <is>
+          <t>API/브라우저로 직접 실행</t>
+        </is>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>outcome CONFIRMED · DepositEvent 1 · 청약 반영</t>
+        </is>
+      </c>
+      <c r="K149" s="3" t="n"/>
+      <c r="L149" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M149" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O149" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P149" s="3" t="inlineStr">
+        <is>
+          <t>REQ-001</t>
+        </is>
+      </c>
+      <c r="Q149" s="3" t="inlineStr">
+        <is>
+          <t>CONFIRMED · DepositEvent 1건 · 청약 COMPLETED</t>
+        </is>
+      </c>
+      <c r="R149" s="3" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>TC-X18</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>F-07</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t>같은 거래번호 재전송</t>
+        </is>
+      </c>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I150" s="3" t="inlineStr">
+        <is>
+          <t>API/브라우저로 직접 실행</t>
+        </is>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>DUPLICATE · 건수 불변</t>
+        </is>
+      </c>
+      <c r="K150" s="3" t="n"/>
+      <c r="L150" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M150" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O150" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P150" s="3" t="inlineStr">
+        <is>
+          <t>REQ-001</t>
+        </is>
+      </c>
+      <c r="Q150" s="3" t="inlineStr">
+        <is>
+          <t>DUPLICATE · 건수 불변(1건)</t>
+        </is>
+      </c>
+      <c r="R150" s="3" t="inlineStr">
+        <is>
+          <t>1순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="n">
+        <v>151</v>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>TC-X19</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>F-07</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>I-03</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>★ 다른 거래번호로 2차 입금</t>
+        </is>
+      </c>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>API/브라우저로 직접 실행</t>
+        </is>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>outcome REVIEW · 발행 불변 · 모집액 불변</t>
+        </is>
+      </c>
+      <c r="K151" s="3" t="n"/>
+      <c r="L151" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M151" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O151" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P151" s="3" t="inlineStr">
+        <is>
+          <t>REQ-001</t>
+        </is>
+      </c>
+      <c r="Q151" s="3" t="inlineStr">
+        <is>
+          <t>REVIEW · 발행 1건 그대로 · 모집액에 1차분만 반영</t>
+        </is>
+      </c>
+      <c r="R151" s="3" t="inlineStr">
+        <is>
+          <t>1순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="n">
+        <v>152</v>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>TC-X20</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>F-07</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>A-01</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>2차 입금이 관리자 검토 큐에 뜬다</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I152" s="3" t="inlineStr">
+        <is>
+          <t>API/브라우저로 직접 실행</t>
+        </is>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>검토 큐에 포함</t>
+        </is>
+      </c>
+      <c r="K152" s="3" t="n"/>
+      <c r="L152" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M152" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O152" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P152" s="3" t="inlineStr">
+        <is>
+          <t>REQ-001</t>
+        </is>
+      </c>
+      <c r="Q152" s="3" t="inlineStr">
+        <is>
+          <t>검토 큐에 포함됨</t>
+        </is>
+      </c>
+      <c r="R152" s="3" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="n">
+        <v>153</v>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>TC-X21</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>F-10</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>/subscriptions</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>내 구독에 죽은 링크가 없다</t>
+        </is>
+      </c>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
+          <t>API/브라우저로 직접 실행</t>
+        </is>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>/investor/payouts 링크 없음 · 404 없음</t>
+        </is>
+      </c>
+      <c r="K153" s="3" t="n"/>
+      <c r="L153" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M153" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O153" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P153" s="3" t="inlineStr">
+        <is>
+          <t>REQ-007</t>
+        </is>
+      </c>
+      <c r="Q153" s="3" t="inlineStr">
+        <is>
+          <t>/investor/payouts 링크 0건 · 404 응답 0건</t>
+        </is>
+      </c>
+      <c r="R153" s="3" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="n">
+        <v>154</v>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>TC-X22</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>F-18</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>mobile 390px 주요 5화면 가로 넘침</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I154" s="3" t="inlineStr">
+        <is>
+          <t>API/브라우저로 직접 실행</t>
+        </is>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>넘침 없음</t>
+        </is>
+      </c>
+      <c r="K154" s="3" t="n"/>
+      <c r="L154" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M154" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O154" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P154" s="3" t="inlineStr">
+        <is>
+          <t>REQ-006</t>
+        </is>
+      </c>
+      <c r="Q154" s="3" t="inlineStr">
+        <is>
+          <t>주요 5화면 모두 390px 이내</t>
+        </is>
+      </c>
+      <c r="R154" s="3" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="n">
+        <v>155</v>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>TC-X23</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>F-18</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>tablet 768px 주요 5화면 가로 넘침</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t>API/브라우저로 직접 실행</t>
+        </is>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>넘침 없음</t>
+        </is>
+      </c>
+      <c r="K155" s="3" t="n"/>
+      <c r="L155" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M155" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O155" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P155" s="3" t="inlineStr">
+        <is>
+          <t>REQ-006</t>
+        </is>
+      </c>
+      <c r="Q155" s="3" t="inlineStr">
+        <is>
+          <t>주요 5화면 모두 768px 이내</t>
+        </is>
+      </c>
+      <c r="R155" s="3" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="n">
+        <v>156</v>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>TC-Y01</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>F-01</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="inlineStr">
+        <is>
+          <t>프로젝트 카드 배지에서 '비보장' 제거</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I156" s="3" t="inlineStr">
+        <is>
+          <t>브라우저로 직접 조작</t>
+        </is>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>'비보장' 없음 · '목표 N%' 유지</t>
+        </is>
+      </c>
+      <c r="K156" s="3" t="n"/>
+      <c r="L156" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M156" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O156" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P156" s="3" t="inlineStr">
+        <is>
+          <t>요청 1</t>
+        </is>
+      </c>
+      <c r="Q156" s="3" t="inlineStr">
+        <is>
+          <t>비보장 미검출 · 목표 배지 유지</t>
+        </is>
+      </c>
+      <c r="R156" s="3" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="n">
+        <v>157</v>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>TC-Y02</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>F-01</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>비회원 홈에서 진행 중 프로젝트 잠금</t>
+        </is>
+      </c>
+      <c r="H157" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I157" s="3" t="inlineStr">
+        <is>
+          <t>브라우저로 직접 조작</t>
+        </is>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>반투명 레이어 + 로그인 버튼 · 카드 클릭해도 이동 안 함</t>
+        </is>
+      </c>
+      <c r="K157" s="3" t="n"/>
+      <c r="L157" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M157" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O157" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P157" s="3" t="inlineStr">
+        <is>
+          <t>요청 2</t>
+        </is>
+      </c>
+      <c r="Q157" s="3" t="inlineStr">
+        <is>
+          <t>오버레이 노출 · 로그인 버튼 2개 · 카드 클릭해도 이동 없음</t>
+        </is>
+      </c>
+      <c r="R157" s="3" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>TC-Y03</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>F-01</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>로그인 후 잠금 해제</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I158" s="3" t="inlineStr">
+        <is>
+          <t>브라우저로 직접 조작</t>
+        </is>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>오버레이 없음 · 카드로 상세 이동</t>
+        </is>
+      </c>
+      <c r="K158" s="3" t="n"/>
+      <c r="L158" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M158" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O158" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P158" s="3" t="inlineStr">
+        <is>
+          <t>요청 2</t>
+        </is>
+      </c>
+      <c r="Q158" s="3" t="inlineStr">
+        <is>
+          <t>오버레이 없음 · /projects/[id] 이동</t>
+        </is>
+      </c>
+      <c r="R158" s="3" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="n">
+        <v>159</v>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>TC-Y04</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>F-04</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>/projects/[id]</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>기준가 카드 문구·값 교체</t>
+        </is>
+      </c>
+      <c r="H159" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I159" s="3" t="inlineStr">
+        <is>
+          <t>브라우저로 직접 조작</t>
+        </is>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>투자 배분 현황 · 내 배분 비율 · 총 배정 토큰 · 내 보유 토큰</t>
+        </is>
+      </c>
+      <c r="K159" s="3" t="n"/>
+      <c r="L159" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M159" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O159" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P159" s="3" t="inlineStr">
+        <is>
+          <t>요청 3</t>
+        </is>
+      </c>
+      <c r="Q159" s="3" t="inlineStr">
+        <is>
+          <t>새 문구 4개 노출 · 옛 문구 4개 미검출</t>
+        </is>
+      </c>
+      <c r="R159" s="3" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>TC-Y05</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>F-04</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>/projects/[id]</t>
+        </is>
+      </c>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="inlineStr">
+        <is>
+          <t>미인증 계정의 신청 버튼 문구</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I160" s="3" t="inlineStr">
+        <is>
+          <t>브라우저로 직접 조작</t>
+        </is>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>'본인확인하고 신청하기'</t>
+        </is>
+      </c>
+      <c r="K160" s="3" t="n"/>
+      <c r="L160" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M160" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O160" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P160" s="3" t="inlineStr">
+        <is>
+          <t>요청 4</t>
+        </is>
+      </c>
+      <c r="Q160" s="3" t="inlineStr">
+        <is>
+          <t>본인확인하고 신청하기</t>
+        </is>
+      </c>
+      <c r="R160" s="3" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="n">
+        <v>161</v>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>TC-Y06</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>F-03</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>/verify</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>신청 → 본인확인 진입 (입력 금액 보존)</t>
+        </is>
+      </c>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I161" s="3" t="inlineStr">
+        <is>
+          <t>브라우저로 직접 조작</t>
+        </is>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>/verify?next=…amount=100000</t>
+        </is>
+      </c>
+      <c r="K161" s="3" t="n"/>
+      <c r="L161" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M161" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N161" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O161" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P161" s="3" t="inlineStr">
+        <is>
+          <t>요청 4</t>
+        </is>
+      </c>
+      <c r="Q161" s="3" t="inlineStr">
+        <is>
+          <t>/verify?next=/projects/[id]/invest/eligibility?amount=100000</t>
+        </is>
+      </c>
+      <c r="R161" s="3" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="n">
+        <v>162</v>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>TC-Y07</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>F-03</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>/verify/mobile-id</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="inlineStr">
+        <is>
+          <t>방법 선택 → 신분증 (next 유지)</t>
+        </is>
+      </c>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I162" s="3" t="inlineStr">
+        <is>
+          <t>브라우저로 직접 조작</t>
+        </is>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>/verify/mobile-id?next=…amount=100000</t>
+        </is>
+      </c>
+      <c r="K162" s="3" t="n"/>
+      <c r="L162" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M162" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O162" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P162" s="3" t="inlineStr">
+        <is>
+          <t>요청 4</t>
+        </is>
+      </c>
+      <c r="Q162" s="3" t="inlineStr">
+        <is>
+          <t>/verify/mobile-id?next=…amount=100000</t>
+        </is>
+      </c>
+      <c r="R162" s="3" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="n">
+        <v>163</v>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>TC-Y08</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>F-03</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>/verify/account</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="inlineStr">
+        <is>
+          <t>계좌 확인 화면에 시연 버튼 존재</t>
+        </is>
+      </c>
+      <c r="H163" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I163" s="3" t="inlineStr">
+        <is>
+          <t>브라우저로 직접 조작</t>
+        </is>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>'시연 넘어가기' 버튼</t>
+        </is>
+      </c>
+      <c r="K163" s="3" t="n"/>
+      <c r="L163" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M163" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N163" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O163" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P163" s="3" t="inlineStr">
+        <is>
+          <t>요청 5</t>
+        </is>
+      </c>
+      <c r="Q163" s="3" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="R163" s="3" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>TC-Y09</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>F-03</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>/verify/account</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>시연 버튼 → 원래 신청으로 복귀</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I164" s="3" t="inlineStr">
+        <is>
+          <t>브라우저로 직접 조작</t>
+        </is>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>next 경로로 이동</t>
+        </is>
+      </c>
+      <c r="K164" s="3" t="n"/>
+      <c r="L164" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M164" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O164" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P164" s="3" t="inlineStr">
+        <is>
+          <t>요청 5</t>
+        </is>
+      </c>
+      <c r="Q164" s="3" t="inlineStr">
+        <is>
+          <t>/projects/[id]/invest/eligibility?amount=100000</t>
+        </is>
+      </c>
+      <c r="R164" s="3" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>TC-Y10</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>F-03</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>/verify/account</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="inlineStr">
+        <is>
+          <t>시연 버튼이 계좌를 실제로 등록한다</t>
+        </is>
+      </c>
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I165" s="3" t="inlineStr">
+        <is>
+          <t>브라우저로 직접 조작</t>
+        </is>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>BankAccount 1건</t>
+        </is>
+      </c>
+      <c r="K165" s="3" t="n"/>
+      <c r="L165" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M165" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N165" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O165" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P165" s="3" t="inlineStr">
+        <is>
+          <t>요청 5</t>
+        </is>
+      </c>
+      <c r="Q165" s="3" t="inlineStr">
+        <is>
+          <t>1건 등록됨</t>
+        </is>
+      </c>
+      <c r="R165" s="3" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="n">
+        <v>166</v>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>TC-Z01</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>I-02</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>/verify/mobile-id</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="inlineStr">
+        <is>
+          <t>모바일 신분증 QR 발급 요청</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>OACX 설정이 있는 프로덕션 · 미인증 시연 계정</t>
+        </is>
+      </c>
+      <c r="I166" s="3" t="inlineStr">
+        <is>
+          <t>1. /verify/mobile-id 진입  2. QR 영역과 /api/identity 응답 확인</t>
+        </is>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>QR 이미지 노출 · '발급하지 못했어요' 문구 없음</t>
+        </is>
+      </c>
+      <c r="K166" s="3" t="inlineStr">
+        <is>
+          <t>서버 로직</t>
+        </is>
+      </c>
+      <c r="L166" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M166" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O166" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P166" s="3" t="inlineStr"/>
+      <c r="Q166" s="3" t="inlineStr">
+        <is>
+          <t>QR 1건 노출 · 실패 문구 0건 · /api/identity/offer 200</t>
+        </is>
+      </c>
+      <c r="R166" s="3" t="inlineStr">
+        <is>
+          <t>1순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>TC-Z02</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>A-13</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>/api/demo/reset</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="inlineStr">
+        <is>
+          <t>데모 리셋이 실제 가입 계정과 본인확인 기록을 남긴다</t>
+        </is>
+      </c>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>실가입 계정 1건(본인확인 기록 5건)이 있는 상태</t>
+        </is>
+      </c>
+      <c r="I167" s="3" t="inlineStr">
+        <is>
+          <t>1. 쓰기 TC 로 시연 데이터를 어지럽힌다  2. 리셋 호출  3. 유저·본인확인 기록 대조</t>
+        </is>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>시드는 원복 · 실가입 계정과 그 본인확인 기록은 보존</t>
+        </is>
+      </c>
+      <c r="K167" s="3" t="inlineStr">
+        <is>
+          <t>서버 로직</t>
+        </is>
+      </c>
+      <c r="L167" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M167" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="inlineStr">
+        <is>
+          <t>API 직접 호출 (프로덕션)</t>
+        </is>
+      </c>
+      <c r="O167" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P167" s="3" t="inlineStr">
+        <is>
+          <t>REQ-008</t>
+        </is>
+      </c>
+      <c r="Q167" s="3" t="inlineStr">
+        <is>
+          <t>실계정 tj041600@naver.com 보존 · 본인확인 5/5 · 전체 유저 8</t>
+        </is>
+      </c>
+      <c r="R167" s="3" t="inlineStr">
+        <is>
+          <t>1순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="n">
+        <v>168</v>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>TC-W02</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>전 화면</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>전 화면</t>
+        </is>
+      </c>
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="inlineStr">
+        <is>
+          <t>주요 10화면 본문에서 명세 금칙어 검사 ('총 배정 토큰·내 보유 토큰'은 명세 18장 예외)</t>
+        </is>
+      </c>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · https://farmfi.co.kr</t>
+        </is>
+      </c>
+      <c r="I168" s="3" t="inlineStr">
+        <is>
+          <t>1. 비회원·투자자 세션으로 10화면 진입  2. 본문에서 STO·지갑 주소·수익 보장 정규식 검사</t>
+        </is>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>검출 0건</t>
+        </is>
+      </c>
+      <c r="K168" s="3" t="inlineStr">
+        <is>
+          <t>화면 로직</t>
+        </is>
+      </c>
+      <c r="L168" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
+      <c r="M168" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N168" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
+      <c r="O168" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="P168" s="3" t="inlineStr"/>
+      <c r="Q168" s="3" t="inlineStr">
+        <is>
+          <t>0건</t>
+        </is>
+      </c>
+      <c r="R168" s="3" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:R132"/>
   <dataValidations count="4">
-    <dataValidation sqref="M2:M132" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M2:M168" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,Blocked,N/A,미실행"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F132" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F168" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"정상,경계,예외"</formula1>
     </dataValidation>
-    <dataValidation sqref="R2:R132" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="R2:R168" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1순위,2순위,3순위"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K132" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K168" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"서버 로직,화면 로직,디자인"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12704,49 +15816,49 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
+          <t>TC-Z02</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>기능 결함</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>2순위</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>데모 리셋이 시드 계정뿐 아니라 실제 가입 계정까지 지운다</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>리셋은 시연 데이터를 최초 상태로 되돌리는 동작이다. 실제로 가입한 계정과 그 계정의 본인확인 기록은 남아야 한다.</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>seedScenario 가 재생성 전에 prisma.user.deleteMany() 로 유저 테이블을 통째로 비운다(seed-scenario.ts:84). 리셋 한 번에 tj041600@naver.com 계정과 거기 붙은 OpenDID 검증 기록 5건이 사라진다. QA 중에는 매 리셋마다 백업했다가 복원해서 이어갔다.</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>관리자 &gt; 데모 리셋</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>기능 결함</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>2순위</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>데모 리셋이 시드 계정뿐 아니라 실제 가입 계정까지 지운다</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>리셋은 시연 데이터를 최초 상태로 되돌리는 동작이다. 실제로 가입한 계정과 그 계정의 본인확인 기록은 남아야 한다.</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>seedScenario 가 재생성 전에 prisma.user.deleteMany() 로 유저 테이블을 통째로 비운다(seed-scenario.ts:84). 리셋 한 번에 tj041600@naver.com 계정과 거기 붙은 OpenDID 검증 기록 5건이 사라진다. QA 중에는 매 리셋마다 백업했다가 복원해서 이어갔다.</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>관리자 &gt; 데모 리셋</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>항상</t>
@@ -12769,13 +15881,17 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>원인 가설: 시드가 멱등하려면 지우고 다시 만드는 게 가장 단순해서 전체 삭제로 짰다. 확인할 것 — 시드 계정만 지울지(`@farmfi.test` 로 한정), 아니면 리셋 범위에서 User 를 빼고 시연 데이터만 되돌릴지. 발표 전 리셋을 한 번이라도 돌릴 계획이면 결정이 필요하다.</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
+          <t>시드가 멱등하려면 지우고 다시 만드는 게 단순해서 유저 테이블을 통째로 비웠다. 시드가 만드는 계정은 전부 @farmfi.test 이므로 삭제 범위를 그 도메인으로 한정하고, 본인확인 기록은 남는 계정의 것만 남겼다(e81d8a05). 3차에서 리셋 후 실계정 1건과 본인확인 5건이 그대로 남는 것을 확인했다(TC-Z02).</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>QA(자동화)</t>
+        </is>
+      </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>확인 전</t>
+          <t>처리 완료</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr"/>
@@ -12784,7 +15900,11 @@
           <t>검수 전</t>
         </is>
       </c>
-      <c r="T9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="U9" s="3" t="inlineStr"/>
     </row>
     <row r="10" ht="88" customHeight="1">
@@ -12918,14 +16038,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
   </cols>
@@ -12953,15 +16073,20 @@
       </c>
       <c r="E1" s="12" t="inlineStr">
         <is>
+          <t>3차 결과</t>
+        </is>
+      </c>
+      <c r="F1" s="12" t="inlineStr">
+        <is>
           <t>담당 A</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>담당 B</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -12986,9 +16111,14 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr"/>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>투자자 세션으로 /admin·/operator 화면이 200 렌더 → 레이아웃 가드 후 자기 역할 홈으로 리다이렉트</t>
         </is>
@@ -13013,9 +16143,14 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr"/>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>31개 중 /api/projects 는 명세 2장에서 비회원 공개. 나머지 30개 중 28개 정상 401, optimization·briefing 2개가 200이었다</t>
         </is>
@@ -13040,9 +16175,14 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr"/>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>54/58 무오류. 나머지 4건은 투자자 세션의 권한 밖 화면 — 3건은 API 403(정상 방어), 1건은 /subscriptions 의 404 → REQ-007</t>
         </is>
@@ -13067,9 +16207,14 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr"/>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>홈 1010px · 프로젝트 568px · 정기구독 546px · 소개 627px → 전부 뷰포트 이내</t>
         </is>
@@ -13094,11 +16239,16 @@
           <t>확인 필요</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>1차 검출 0건. 요청 3으로 '총 배정 토큰·내 보유 토큰' 라벨이 들어가 다음 라운드에서 이 기준을 다시 본다</t>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>1차 검출 0건. 요청 3으로 '총 배정 토큰·내 보유 토큰' 라벨이 들어가, 3차에서 그 둘을 명세 18장 예외로 두고 다시 검사했다 — 0건</t>
         </is>
       </c>
     </row>
@@ -13121,9 +16271,14 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr"/>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>명세 14장 오류 코드 문구 — 400/403 응답 모두 한국어 사유 포함</t>
         </is>
@@ -13148,11 +16303,16 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr"/>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>/api/demo/reset 으로 모집액·발행·입금 기록 원복 확인. 실계정과 KYC 기록은 백업 후 복원</t>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>/api/demo/reset 으로 모집액·발행·입금 기록 원복 확인. 3차부터는 리셋이 시드 계정만 지우므로 실계정과 본인확인 기록을 백업할 필요가 없다(REQ-008).</t>
         </is>
       </c>
     </row>

--- a/docs/qa/web-qa-sheet.xlsx
+++ b/docs/qa/web-qa-sheet.xlsx
@@ -786,27 +786,27 @@
     </row>
     <row r="13">
       <c r="A13" s="7">
-        <f>COUNTA('TC 시나리오'!B2:B168)</f>
+        <f>COUNTA('TC 시나리오'!B2:B169)</f>
         <v/>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF('TC 시나리오'!M2:M168,"Pass")</f>
+        <f>COUNTIF('TC 시나리오'!L2:L169,"Pass")</f>
         <v/>
       </c>
       <c r="C13" s="7">
-        <f>COUNTIF('TC 시나리오'!M2:M168,"Fail")</f>
+        <f>COUNTIF('TC 시나리오'!L2:L169,"Fail")</f>
         <v/>
       </c>
       <c r="D13" s="7">
-        <f>COUNTIF('TC 시나리오'!M2:M168,"Blocked")</f>
+        <f>COUNTIF('TC 시나리오'!L2:L169,"Blocked")</f>
         <v/>
       </c>
       <c r="E13" s="7">
-        <f>COUNTIF('TC 시나리오'!M2:M168,"N/A")</f>
+        <f>COUNTIF('TC 시나리오'!L2:L169,"N/A")</f>
         <v/>
       </c>
       <c r="F13" s="7">
-        <f>COUNTIF('TC 시나리오'!M2:M168,"미실행")</f>
+        <f>COUNTIF('TC 시나리오'!L2:L169,"미실행")</f>
         <v/>
       </c>
       <c r="G13" s="7">
@@ -871,19 +871,19 @@
         <v/>
       </c>
       <c r="B18" s="7">
-        <f>COUNTIF('요청사항(REQ)'!Q2:Q10,"확인 전")</f>
+        <f>COUNTIF('요청사항(REQ)'!O2:O10,"확인 전")</f>
         <v/>
       </c>
       <c r="C18" s="7">
-        <f>COUNTIF('요청사항(REQ)'!Q2:Q10,"처리 중")</f>
+        <f>COUNTIF('요청사항(REQ)'!O2:O10,"처리 중")</f>
         <v/>
       </c>
       <c r="D18" s="7">
-        <f>COUNTIF('요청사항(REQ)'!Q2:Q10,"처리 완료")</f>
+        <f>COUNTIF('요청사항(REQ)'!O2:O10,"처리 완료")</f>
         <v/>
       </c>
       <c r="E18" s="7">
-        <f>COUNTIF('요청사항(REQ)'!S2:S10,"검수 완료")</f>
+        <f>COUNTIF('요청사항(REQ)'!P2:P10,"검수 완료")</f>
         <v/>
       </c>
       <c r="F18" s="7">
@@ -1120,7 +1120,7 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>① 코드·일시·담당자 공란 불가</t>
+          <t>① 코드·일시 공란 불가</t>
         </is>
       </c>
     </row>
@@ -1155,23 +1155,19 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>⑥ 담당자와 검수자는 같은 사람일 수 없다</t>
+          <t>⑥ 크로스 시트는 자기 열만 채운다</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>⑦ 크로스 시트는 자기 열만 채운다</t>
+          <t>⑦ TC 밖에서 발견한 것도 REQ 로 등록한다</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>⑧ TC 밖에서 발견한 것도 REQ 로 등록한다</t>
-        </is>
-      </c>
+      <c r="A38" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -1343,7 +1339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R168"/>
+  <dimension ref="A1:Q169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1357,12 +1353,12 @@
     <col width="26" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="58" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="58" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
     <col width="9" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
@@ -1424,35 +1420,30 @@
       </c>
       <c r="L1" s="12" t="inlineStr">
         <is>
-          <t>배정 테스터</t>
+          <t>판정</t>
         </is>
       </c>
       <c r="M1" s="12" t="inlineStr">
         <is>
-          <t>판정</t>
+          <t>테스트 환경</t>
         </is>
       </c>
       <c r="N1" s="12" t="inlineStr">
         <is>
-          <t>테스트 환경</t>
+          <t>테스트 일시</t>
         </is>
       </c>
       <c r="O1" s="12" t="inlineStr">
         <is>
-          <t>테스트 일시</t>
+          <t>연결 요청 코드</t>
         </is>
       </c>
       <c r="P1" s="12" t="inlineStr">
         <is>
-          <t>연결 요청 코드</t>
+          <t>비고 (실제 관측값)</t>
         </is>
       </c>
       <c r="Q1" s="12" t="inlineStr">
-        <is>
-          <t>비고 (실제 관측값)</t>
-        </is>
-      </c>
-      <c r="R1" s="12" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
@@ -1508,29 +1499,28 @@
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr"/>
-      <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L2" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr"/>
+      <c r="O2" s="3" t="inlineStr"/>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -1586,29 +1576,28 @@
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr"/>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -1664,29 +1653,28 @@
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr"/>
+      <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -1742,29 +1730,28 @@
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr"/>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -1820,29 +1807,28 @@
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr"/>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R6" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -1898,29 +1884,28 @@
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -1976,29 +1961,28 @@
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L8" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P8" s="3" t="inlineStr"/>
+      <c r="O8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -2054,29 +2038,28 @@
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L9" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q9" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -2132,29 +2115,28 @@
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L10" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P10" s="3" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -2210,29 +2192,28 @@
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr"/>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -2288,29 +2269,28 @@
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr"/>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L12" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P12" s="3" t="inlineStr"/>
+      <c r="O12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R12" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -2366,29 +2346,28 @@
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr"/>
-      <c r="L13" s="3" t="inlineStr"/>
-      <c r="M13" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L13" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q13" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R13" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -2444,29 +2423,28 @@
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr"/>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L14" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -2522,29 +2500,28 @@
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr"/>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L15" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q15" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -2600,29 +2577,28 @@
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr"/>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L16" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P16" s="3" t="inlineStr"/>
+      <c r="O16" s="3" t="inlineStr"/>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q16" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R16" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -2678,29 +2654,28 @@
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L17" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P17" s="3" t="inlineStr"/>
+      <c r="O17" s="3" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -2756,29 +2731,28 @@
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr"/>
-      <c r="L18" s="3" t="inlineStr"/>
-      <c r="M18" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L18" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P18" s="3" t="inlineStr"/>
+      <c r="O18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -2834,29 +2808,28 @@
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr"/>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L19" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -2912,29 +2885,28 @@
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr"/>
-      <c r="L20" s="3" t="inlineStr"/>
-      <c r="M20" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L20" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P20" s="3" t="inlineStr"/>
+      <c r="O20" s="3" t="inlineStr"/>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q20" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R20" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -2990,33 +2962,32 @@
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr"/>
-      <c r="L21" s="3" t="inlineStr"/>
-      <c r="M21" s="14" t="inlineStr">
+      <c r="L21" s="14" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-007</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>REQ-007</t>
+          <t>HTTP 200 · 콘솔오류 1건 · 네트워크 404 /investor/payouts?_rsc=14v5l</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200 · 콘솔오류 1건 · 네트워크 404 /investor/payouts?_rsc=14v5l</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -3072,29 +3043,28 @@
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr"/>
-      <c r="L22" s="3" t="inlineStr"/>
-      <c r="M22" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L22" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P22" s="3" t="inlineStr"/>
+      <c r="O22" s="3" t="inlineStr"/>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q22" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R22" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -3150,33 +3120,32 @@
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr"/>
-      <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="14" t="inlineStr">
+      <c r="L23" s="14" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-004</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>REQ-004</t>
+          <t>HTTP 200</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -3232,33 +3201,32 @@
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="3" t="inlineStr"/>
-      <c r="M24" s="14" t="inlineStr">
+      <c r="L24" s="14" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-004</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>REQ-004</t>
+          <t>HTTP 200 · 콘솔오류 2건 · 네트워크 403 /api/audit-logs; 403 /api/audit-logs?format=csv&amp;_rsc=1lpe3</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200 · 콘솔오류 2건 · 네트워크 403 /api/audit-logs; 403 /api/audit-logs?format=csv&amp;_rsc=1lpe3</t>
-        </is>
-      </c>
-      <c r="R24" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -3314,33 +3282,32 @@
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr"/>
-      <c r="L25" s="3" t="inlineStr"/>
-      <c r="M25" s="14" t="inlineStr">
+      <c r="L25" s="14" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-004</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>REQ-004</t>
+          <t>HTTP 200 · 콘솔오류 1건 · 네트워크 403 /api/appeals?milestoneId=cmt6qy0kz04n8esudho8mb3l8</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200 · 콘솔오류 1건 · 네트워크 403 /api/appeals?milestoneId=cmt6qy0kz04n8esudho8mb3l8</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -3396,33 +3363,32 @@
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr"/>
-      <c r="L26" s="3" t="inlineStr"/>
-      <c r="M26" s="14" t="inlineStr">
+      <c r="L26" s="14" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-004</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>REQ-004</t>
+          <t>HTTP 200 · 콘솔오류 2건 · 네트워크 403 /api/admin/projects/cmt6qxvrf000pesud96j1e56u/records?period=2026-08; 403 /api/sales?projectId=cmt6qxvrf000pesud96j1e56u&amp;days=90</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200 · 콘솔오류 2건 · 네트워크 403 /api/admin/projects/cmt6qxvrf000pesud96j1e56u/records?period=2026-08; 403 /api/sales?projectId=cmt6qxvrf000pesud96j1e56u&amp;days=90</t>
-        </is>
-      </c>
-      <c r="R26" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -3478,29 +3444,28 @@
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr"/>
-      <c r="L27" s="3" t="inlineStr"/>
-      <c r="M27" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L27" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P27" s="3" t="inlineStr"/>
+      <c r="O27" s="3" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -3556,29 +3521,28 @@
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr"/>
-      <c r="L28" s="3" t="inlineStr"/>
-      <c r="M28" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L28" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P28" s="3" t="inlineStr"/>
+      <c r="O28" s="3" t="inlineStr"/>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q28" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -3634,29 +3598,28 @@
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="3" t="inlineStr"/>
-      <c r="M29" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L29" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P29" s="3" t="inlineStr"/>
+      <c r="O29" s="3" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -3712,29 +3675,28 @@
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr"/>
-      <c r="L30" s="3" t="inlineStr"/>
-      <c r="M30" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L30" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P30" s="3" t="inlineStr"/>
+      <c r="O30" s="3" t="inlineStr"/>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q30" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R30" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -3790,29 +3752,28 @@
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="inlineStr"/>
-      <c r="M31" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L31" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P31" s="3" t="inlineStr"/>
+      <c r="O31" s="3" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q31" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R31" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -3868,29 +3829,28 @@
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr"/>
-      <c r="L32" s="3" t="inlineStr"/>
-      <c r="M32" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L32" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P32" s="3" t="inlineStr"/>
+      <c r="O32" s="3" t="inlineStr"/>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -3946,29 +3906,28 @@
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr"/>
-      <c r="L33" s="3" t="inlineStr"/>
-      <c r="M33" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L33" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P33" s="3" t="inlineStr"/>
+      <c r="O33" s="3" t="inlineStr"/>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -4024,29 +3983,28 @@
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr"/>
-      <c r="L34" s="3" t="inlineStr"/>
-      <c r="M34" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L34" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P34" s="3" t="inlineStr"/>
+      <c r="O34" s="3" t="inlineStr"/>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q34" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R34" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -4102,29 +4060,28 @@
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr"/>
-      <c r="L35" s="3" t="inlineStr"/>
-      <c r="M35" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L35" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P35" s="3" t="inlineStr"/>
+      <c r="O35" s="3" t="inlineStr"/>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -4180,29 +4137,28 @@
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr"/>
-      <c r="L36" s="3" t="inlineStr"/>
-      <c r="M36" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L36" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P36" s="3" t="inlineStr"/>
+      <c r="O36" s="3" t="inlineStr"/>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q36" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R36" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -4258,29 +4214,28 @@
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr"/>
-      <c r="L37" s="3" t="inlineStr"/>
-      <c r="M37" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L37" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P37" s="3" t="inlineStr"/>
+      <c r="O37" s="3" t="inlineStr"/>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q37" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R37" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -4336,29 +4291,28 @@
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="3" t="inlineStr"/>
-      <c r="M38" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L38" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P38" s="3" t="inlineStr"/>
+      <c r="O38" s="3" t="inlineStr"/>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q38" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -4414,29 +4368,28 @@
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr"/>
-      <c r="L39" s="3" t="inlineStr"/>
-      <c r="M39" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L39" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P39" s="3" t="inlineStr"/>
+      <c r="O39" s="3" t="inlineStr"/>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q39" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R39" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -4492,29 +4445,28 @@
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr"/>
-      <c r="L40" s="3" t="inlineStr"/>
-      <c r="M40" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L40" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P40" s="3" t="inlineStr"/>
+      <c r="O40" s="3" t="inlineStr"/>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R40" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -4570,29 +4522,28 @@
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr"/>
-      <c r="L41" s="3" t="inlineStr"/>
-      <c r="M41" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L41" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P41" s="3" t="inlineStr"/>
+      <c r="O41" s="3" t="inlineStr"/>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -4648,29 +4599,28 @@
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr"/>
-      <c r="L42" s="3" t="inlineStr"/>
-      <c r="M42" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L42" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P42" s="3" t="inlineStr"/>
+      <c r="O42" s="3" t="inlineStr"/>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q42" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -4726,29 +4676,28 @@
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr"/>
-      <c r="L43" s="3" t="inlineStr"/>
-      <c r="M43" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L43" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P43" s="3" t="inlineStr"/>
+      <c r="O43" s="3" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -4804,29 +4753,28 @@
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr"/>
-      <c r="L44" s="3" t="inlineStr"/>
-      <c r="M44" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L44" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -4882,29 +4830,28 @@
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr"/>
-      <c r="L45" s="3" t="inlineStr"/>
-      <c r="M45" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L45" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P45" s="3" t="inlineStr"/>
+      <c r="O45" s="3" t="inlineStr"/>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q45" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -4960,29 +4907,28 @@
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="3" t="inlineStr"/>
-      <c r="M46" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L46" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P46" s="3" t="inlineStr"/>
+      <c r="O46" s="3" t="inlineStr"/>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -5038,29 +4984,28 @@
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr"/>
-      <c r="L47" s="3" t="inlineStr"/>
-      <c r="M47" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L47" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P47" s="3" t="inlineStr"/>
+      <c r="O47" s="3" t="inlineStr"/>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q47" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R47" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -5116,29 +5061,28 @@
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr"/>
-      <c r="L48" s="3" t="inlineStr"/>
-      <c r="M48" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L48" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P48" s="3" t="inlineStr"/>
+      <c r="O48" s="3" t="inlineStr"/>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q48" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R48" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -5194,29 +5138,28 @@
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr"/>
-      <c r="L49" s="3" t="inlineStr"/>
-      <c r="M49" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L49" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P49" s="3" t="inlineStr"/>
+      <c r="O49" s="3" t="inlineStr"/>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q49" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R49" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -5272,29 +5215,28 @@
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr"/>
-      <c r="L50" s="3" t="inlineStr"/>
-      <c r="M50" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L50" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P50" s="3" t="inlineStr"/>
+      <c r="O50" s="3" t="inlineStr"/>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q50" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R50" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -5350,29 +5292,28 @@
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr"/>
-      <c r="L51" s="3" t="inlineStr"/>
-      <c r="M51" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L51" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P51" s="3" t="inlineStr"/>
+      <c r="O51" s="3" t="inlineStr"/>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q51" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R51" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -5428,29 +5369,28 @@
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr"/>
-      <c r="L52" s="3" t="inlineStr"/>
-      <c r="M52" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L52" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P52" s="3" t="inlineStr"/>
+      <c r="O52" s="3" t="inlineStr"/>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q52" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R52" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -5506,29 +5446,28 @@
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr"/>
-      <c r="L53" s="3" t="inlineStr"/>
-      <c r="M53" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L53" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O53" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P53" s="3" t="inlineStr"/>
+      <c r="O53" s="3" t="inlineStr"/>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q53" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R53" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -5584,29 +5523,28 @@
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr"/>
-      <c r="L54" s="3" t="inlineStr"/>
-      <c r="M54" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L54" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P54" s="3" t="inlineStr"/>
+      <c r="O54" s="3" t="inlineStr"/>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q54" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R54" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -5662,29 +5600,28 @@
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr"/>
-      <c r="L55" s="3" t="inlineStr"/>
-      <c r="M55" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L55" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P55" s="3" t="inlineStr"/>
+      <c r="O55" s="3" t="inlineStr"/>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q55" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R55" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -5740,29 +5677,28 @@
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr"/>
-      <c r="L56" s="3" t="inlineStr"/>
-      <c r="M56" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L56" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O56" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P56" s="3" t="inlineStr"/>
+      <c r="O56" s="3" t="inlineStr"/>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q56" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R56" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -5818,29 +5754,28 @@
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr"/>
-      <c r="L57" s="3" t="inlineStr"/>
-      <c r="M57" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L57" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O57" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P57" s="3" t="inlineStr"/>
+      <c r="O57" s="3" t="inlineStr"/>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q57" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R57" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -5896,29 +5831,28 @@
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr"/>
-      <c r="L58" s="3" t="inlineStr"/>
-      <c r="M58" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L58" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O58" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P58" s="3" t="inlineStr"/>
+      <c r="O58" s="3" t="inlineStr"/>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q58" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R58" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -5974,29 +5908,28 @@
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr"/>
-      <c r="L59" s="3" t="inlineStr"/>
-      <c r="M59" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L59" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O59" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P59" s="3" t="inlineStr"/>
+      <c r="O59" s="3" t="inlineStr"/>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
       <c r="Q59" s="3" t="inlineStr">
-        <is>
-          <t>HTTP 200</t>
-        </is>
-      </c>
-      <c r="R59" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -6052,29 +5985,28 @@
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr"/>
-      <c r="L60" s="3" t="inlineStr"/>
-      <c r="M60" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L60" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O60" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P60" s="3" t="inlineStr"/>
+      <c r="O60" s="3" t="inlineStr"/>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>guest:401 / investor:403 / operator:403 / landlord:403 / admin:200</t>
+        </is>
+      </c>
       <c r="Q60" s="3" t="inlineStr">
-        <is>
-          <t>guest:401 / investor:403 / operator:403 / landlord:403 / admin:200</t>
-        </is>
-      </c>
-      <c r="R60" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -6130,29 +6062,28 @@
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr"/>
-      <c r="L61" s="3" t="inlineStr"/>
-      <c r="M61" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L61" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O61" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P61" s="3" t="inlineStr"/>
+      <c r="O61" s="3" t="inlineStr"/>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>guest:401 / investor:403 / operator:403 / landlord:403 / admin:200</t>
+        </is>
+      </c>
       <c r="Q61" s="3" t="inlineStr">
-        <is>
-          <t>guest:401 / investor:403 / operator:403 / landlord:403 / admin:200</t>
-        </is>
-      </c>
-      <c r="R61" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -6208,29 +6139,28 @@
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr"/>
-      <c r="L62" s="3" t="inlineStr"/>
-      <c r="M62" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L62" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O62" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P62" s="3" t="inlineStr"/>
+      <c r="O62" s="3" t="inlineStr"/>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>guest:401 / investor:403 / operator:403 / landlord:403 / admin:200</t>
+        </is>
+      </c>
       <c r="Q62" s="3" t="inlineStr">
-        <is>
-          <t>guest:401 / investor:403 / operator:403 / landlord:403 / admin:200</t>
-        </is>
-      </c>
-      <c r="R62" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -6286,29 +6216,28 @@
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr"/>
-      <c r="L63" s="3" t="inlineStr"/>
-      <c r="M63" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L63" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O63" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P63" s="3" t="inlineStr"/>
+      <c r="O63" s="3" t="inlineStr"/>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>guest:401 / investor:403 / operator:403 / landlord:403 / admin:200</t>
+        </is>
+      </c>
       <c r="Q63" s="3" t="inlineStr">
-        <is>
-          <t>guest:401 / investor:403 / operator:403 / landlord:403 / admin:200</t>
-        </is>
-      </c>
-      <c r="R63" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -6364,29 +6293,28 @@
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr"/>
-      <c r="L64" s="3" t="inlineStr"/>
-      <c r="M64" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L64" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O64" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P64" s="3" t="inlineStr"/>
+      <c r="O64" s="3" t="inlineStr"/>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>guest:401 / investor:403 / operator:403 / landlord:403 / admin:200</t>
+        </is>
+      </c>
       <c r="Q64" s="3" t="inlineStr">
-        <is>
-          <t>guest:401 / investor:403 / operator:403 / landlord:403 / admin:200</t>
-        </is>
-      </c>
-      <c r="R64" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -6442,33 +6370,32 @@
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr"/>
-      <c r="L65" s="3" t="inlineStr"/>
-      <c r="M65" s="14" t="inlineStr">
+      <c r="L65" s="14" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-005</t>
         </is>
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
-          <t>REQ-005</t>
+          <t>200 {"project":{"id":"cmt6qxvrf000pesud96j1e56u","name":"온천장 스마트팜 1호점"},"crop":{"key":"leafy","label":"엽채류(상추)","dliTarget":15},"inputs":{"cropKey":"leafy","tar | 명세 7장: 배정되지 않은 지점의 데이터는 보이지 않는다</t>
         </is>
       </c>
       <c r="Q65" s="3" t="inlineStr">
-        <is>
-          <t>200 {"project":{"id":"cmt6qxvrf000pesud96j1e56u","name":"온천장 스마트팜 1호점"},"crop":{"key":"leafy","label":"엽채류(상추)","dliTarget":15},"inputs":{"cropKey":"leafy","tar | 명세 7장: 배정되지 않은 지점의 데이터는 보이지 않는다</t>
-        </is>
-      </c>
-      <c r="R65" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -6524,33 +6451,32 @@
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr"/>
-      <c r="L66" s="3" t="inlineStr"/>
-      <c r="M66" s="14" t="inlineStr">
+      <c r="L66" s="14" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-005</t>
         </is>
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
-          <t>REQ-005</t>
+          <t>200 {"project":{"id":"cmt6qxvrf000pesud96j1e56u","name":"온천장 스마트팜 1호점"},"generatedAt":"2026-08-24T16:36:28.966Z","briefing":{"items":[{"priority":"high","catego | 발주 수량·수요 예측 등 운영 정보 포함</t>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
-        <is>
-          <t>200 {"project":{"id":"cmt6qxvrf000pesud96j1e56u","name":"온천장 스마트팜 1호점"},"generatedAt":"2026-08-24T16:36:28.966Z","briefing":{"items":[{"priority":"high","catego | 발주 수량·수요 예측 등 운영 정보 포함</t>
-        </is>
-      </c>
-      <c r="R66" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -6606,29 +6532,28 @@
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr"/>
-      <c r="L67" s="3" t="inlineStr"/>
-      <c r="M67" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L67" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O67" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P67" s="3" t="inlineStr"/>
+      <c r="O67" s="3" t="inlineStr"/>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>403 {"error":"운영자만 증빙을 제출할 수 있습니다."}</t>
+        </is>
+      </c>
       <c r="Q67" s="3" t="inlineStr">
-        <is>
-          <t>403 {"error":"운영자만 증빙을 제출할 수 있습니다."}</t>
-        </is>
-      </c>
-      <c r="R67" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -6684,29 +6609,28 @@
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr"/>
-      <c r="L68" s="3" t="inlineStr"/>
-      <c r="M68" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L68" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O68" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P68" s="3" t="inlineStr"/>
+      <c r="O68" s="3" t="inlineStr"/>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>403 {"error":"Forbidden"}</t>
+        </is>
+      </c>
       <c r="Q68" s="3" t="inlineStr">
-        <is>
-          <t>403 {"error":"Forbidden"}</t>
-        </is>
-      </c>
-      <c r="R68" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -6762,29 +6686,28 @@
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr"/>
-      <c r="L69" s="3" t="inlineStr"/>
-      <c r="M69" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L69" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O69" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P69" s="3" t="inlineStr"/>
+      <c r="O69" s="3" t="inlineStr"/>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>403 {"error":"Forbidden"}</t>
+        </is>
+      </c>
       <c r="Q69" s="3" t="inlineStr">
-        <is>
-          <t>403 {"error":"Forbidden"}</t>
-        </is>
-      </c>
-      <c r="R69" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -6840,29 +6763,28 @@
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr"/>
-      <c r="L70" s="3" t="inlineStr"/>
-      <c r="M70" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L70" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O70" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P70" s="3" t="inlineStr"/>
+      <c r="O70" s="3" t="inlineStr"/>
+      <c r="P70" s="3" t="inlineStr">
+        <is>
+          <t>403 {"error":"Forbidden"}</t>
+        </is>
+      </c>
       <c r="Q70" s="3" t="inlineStr">
-        <is>
-          <t>403 {"error":"Forbidden"}</t>
-        </is>
-      </c>
-      <c r="R70" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -6918,29 +6840,28 @@
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr"/>
-      <c r="L71" s="3" t="inlineStr"/>
-      <c r="M71" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L71" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O71" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P71" s="3" t="inlineStr"/>
+      <c r="O71" s="3" t="inlineStr"/>
+      <c r="P71" s="3" t="inlineStr">
+        <is>
+          <t>400 {"error":"증빙이 승인된 단계만 집행할 수 있습니다."} | 명세 18장 권한 인수 테스트 항목</t>
+        </is>
+      </c>
       <c r="Q71" s="3" t="inlineStr">
-        <is>
-          <t>400 {"error":"증빙이 승인된 단계만 집행할 수 있습니다."} | 명세 18장 권한 인수 테스트 항목</t>
-        </is>
-      </c>
-      <c r="R71" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -6996,29 +6917,28 @@
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr"/>
-      <c r="L72" s="3" t="inlineStr"/>
-      <c r="M72" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L72" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O72" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P72" s="3" t="inlineStr"/>
+      <c r="O72" s="3" t="inlineStr"/>
+      <c r="P72" s="3" t="inlineStr">
+        <is>
+          <t>400 {"error":"아직 판정하지 않은 항목이 있습니다 — 계약서 · 영수증 · 현장 사진 · 교차검증"} | 명세 A-08: 한 항목이라도 미지정이면 승인할 수 없다</t>
+        </is>
+      </c>
       <c r="Q72" s="3" t="inlineStr">
-        <is>
-          <t>400 {"error":"아직 판정하지 않은 항목이 있습니다 — 계약서 · 영수증 · 현장 사진 · 교차검증"} | 명세 A-08: 한 항목이라도 미지정이면 승인할 수 없다</t>
-        </is>
-      </c>
-      <c r="R72" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -7074,29 +6994,28 @@
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr"/>
-      <c r="L73" s="3" t="inlineStr"/>
-      <c r="M73" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L73" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O73" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P73" s="3" t="inlineStr"/>
+      <c r="O73" s="3" t="inlineStr"/>
+      <c r="P73" s="3" t="inlineStr">
+        <is>
+          <t>200 status=evidence_submitted</t>
+        </is>
+      </c>
       <c r="Q73" s="3" t="inlineStr">
-        <is>
-          <t>200 status=evidence_submitted</t>
-        </is>
-      </c>
-      <c r="R73" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -7152,29 +7071,28 @@
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr"/>
-      <c r="L74" s="3" t="inlineStr"/>
-      <c r="M74" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L74" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O74" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P74" s="3" t="inlineStr"/>
+      <c r="O74" s="3" t="inlineStr"/>
+      <c r="P74" s="3" t="inlineStr">
+        <is>
+          <t>403 {"error":"이 지점의 운영자만 제출할 수 있습니다."} | QA 픽스처 운영자 계정 사용 — 리셋으로 제거</t>
+        </is>
+      </c>
       <c r="Q74" s="3" t="inlineStr">
-        <is>
-          <t>403 {"error":"이 지점의 운영자만 제출할 수 있습니다."} | QA 픽스처 운영자 계정 사용 — 리셋으로 제거</t>
-        </is>
-      </c>
-      <c r="R74" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -7230,33 +7148,32 @@
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr"/>
-      <c r="L75" s="3" t="inlineStr"/>
-      <c r="M75" s="14" t="inlineStr">
+      <c r="L75" s="14" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-003</t>
         </is>
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
-          <t>REQ-003</t>
+          <t>200 {"milestone":{"id":"qa_ms_unassigned","projectId":"qa_proj_unassigned","seq":1,"name":"QA 공간 준비","description":null,"releasePct":3500,"releaseAmount":0,"status":"evidence_submitted","conditionText":null,"requiredSignals":[],"iotMinDays":0,"retryCount":0,"cross | 단계 상태=evidence_submitted | 명세 O-11 마지막 줄</t>
         </is>
       </c>
       <c r="Q75" s="3" t="inlineStr">
-        <is>
-          <t>200 {"milestone":{"id":"qa_ms_unassigned","projectId":"qa_proj_unassigned","seq":1,"name":"QA 공간 준비","description":null,"releasePct":3500,"releaseAmount":0,"status":"evidence_submitted","conditionText":null,"requiredSignals":[],"iotMinDays":0,"retryCount":0,"cross | 단계 상태=evidence_submitted | 명세 O-11 마지막 줄</t>
-        </is>
-      </c>
-      <c r="R75" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -7312,29 +7229,28 @@
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr"/>
-      <c r="L76" s="3" t="inlineStr"/>
-      <c r="M76" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L76" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O76" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P76" s="3" t="inlineStr"/>
+      <c r="O76" s="3" t="inlineStr"/>
+      <c r="P76" s="3" t="inlineStr">
+        <is>
+          <t>400 {"error":"신청 금액을 확인해 주세요."}</t>
+        </is>
+      </c>
       <c r="Q76" s="3" t="inlineStr">
-        <is>
-          <t>400 {"error":"신청 금액을 확인해 주세요."}</t>
-        </is>
-      </c>
-      <c r="R76" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -7390,29 +7306,28 @@
         </is>
       </c>
       <c r="K77" s="3" t="inlineStr"/>
-      <c r="L77" s="3" t="inlineStr"/>
-      <c r="M77" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L77" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O77" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P77" s="3" t="inlineStr"/>
+      <c r="O77" s="3" t="inlineStr"/>
+      <c r="P77" s="3" t="inlineStr">
+        <is>
+          <t>200 id=cmt7gicr2000104l7if5g8per status=DRAFT</t>
+        </is>
+      </c>
       <c r="Q77" s="3" t="inlineStr">
-        <is>
-          <t>200 id=cmt7gicr2000104l7if5g8per status=DRAFT</t>
-        </is>
-      </c>
-      <c r="R77" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -7468,29 +7383,28 @@
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr"/>
-      <c r="L78" s="3" t="inlineStr"/>
-      <c r="M78" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L78" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O78" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P78" s="3" t="inlineStr"/>
+      <c r="O78" s="3" t="inlineStr"/>
+      <c r="P78" s="3" t="inlineStr">
+        <is>
+          <t>200 {"investment":{"id":"cmt7gicr2000104l7if5g8per","userId":"cmt6qxu8q0009esudda86j6f4","projectId":"cmt6qy0rt04nfesudctnt7vow","status":"ELIGIBILITY_CHECKED","amount":1000000,"units"</t>
+        </is>
+      </c>
       <c r="Q78" s="3" t="inlineStr">
-        <is>
-          <t>200 {"investment":{"id":"cmt7gicr2000104l7if5g8per","userId":"cmt6qxu8q0009esudda86j6f4","projectId":"cmt6qy0rt04nfesudctnt7vow","status":"ELIGIBILITY_CHECKED","amount":1000000,"units"</t>
-        </is>
-      </c>
-      <c r="R78" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -7546,29 +7460,28 @@
         </is>
       </c>
       <c r="K79" s="3" t="inlineStr"/>
-      <c r="L79" s="3" t="inlineStr"/>
-      <c r="M79" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L79" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O79" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P79" s="3" t="inlineStr"/>
+      <c r="O79" s="3" t="inlineStr"/>
+      <c r="P79" s="3" t="inlineStr">
+        <is>
+          <t>문서[investment_contract:200 risk_disclosure:200 privacy_consent:200] 계약 200 {"investment":{"id":"cmt7gicr2000104l7if5g8per","userId":"cmt6qxu8q0009esudda86j6f4","projectId":"cmt6qy0rt04nfesudctnt7vow","status":"AWAITING_DEPOSIT","amount":1000000,"units":100,"eligible":true,"eligibilityMemo":"신청 가능합니다.","annualLimit":20000000,"consente</t>
+        </is>
+      </c>
       <c r="Q79" s="3" t="inlineStr">
-        <is>
-          <t>문서[investment_contract:200 risk_disclosure:200 privacy_consent:200] 계약 200 {"investment":{"id":"cmt7gicr2000104l7if5g8per","userId":"cmt6qxu8q0009esudda86j6f4","projectId":"cmt6qy0rt04nfesudctnt7vow","status":"AWAITING_DEPOSIT","amount":1000000,"units":100,"eligible":true,"eligibilityMemo":"신청 가능합니다.","annualLimit":20000000,"consente</t>
-        </is>
-      </c>
-      <c r="R79" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -7624,29 +7537,28 @@
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr"/>
-      <c r="L80" s="3" t="inlineStr"/>
-      <c r="M80" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L80" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O80" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P80" s="3" t="inlineStr"/>
+      <c r="O80" s="3" t="inlineStr"/>
+      <c r="P80" s="3" t="inlineStr">
+        <is>
+          <t>400 {"error":"서명을 입력해 주세요."}</t>
+        </is>
+      </c>
       <c r="Q80" s="3" t="inlineStr">
-        <is>
-          <t>400 {"error":"서명을 입력해 주세요."}</t>
-        </is>
-      </c>
-      <c r="R80" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -7702,29 +7614,28 @@
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr"/>
-      <c r="L81" s="3" t="inlineStr"/>
-      <c r="M81" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L81" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N81" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O81" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P81" s="3" t="inlineStr"/>
+      <c r="O81" s="3" t="inlineStr"/>
+      <c r="P81" s="3" t="inlineStr">
+        <is>
+          <t>200 status=AWAITING_DEPOSIT bank=우리은행 | {"virtualAccount":{"bankName":"우리은행","accountNumber":"X6516729718003","holderName":"팜피 투자금 분리보관 계정","amount":1000000,"expiresAt":"2026-08-25T16:36:55.000Z"}}</t>
+        </is>
+      </c>
       <c r="Q81" s="3" t="inlineStr">
-        <is>
-          <t>200 status=AWAITING_DEPOSIT bank=우리은행 | {"virtualAccount":{"bankName":"우리은행","accountNumber":"X6516729718003","holderName":"팜피 투자금 분리보관 계정","amount":1000000,"expiresAt":"2026-08-25T16:36:55.000Z"}}</t>
-        </is>
-      </c>
-      <c r="R81" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -7780,29 +7691,28 @@
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr"/>
-      <c r="L82" s="3" t="inlineStr"/>
-      <c r="M82" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L82" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O82" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P82" s="3" t="inlineStr"/>
+      <c r="O82" s="3" t="inlineStr"/>
+      <c r="P82" s="3" t="inlineStr">
+        <is>
+          <t>401 {"error":"Invalid secret"}</t>
+        </is>
+      </c>
       <c r="Q82" s="3" t="inlineStr">
-        <is>
-          <t>401 {"error":"Invalid secret"}</t>
-        </is>
-      </c>
-      <c r="R82" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -7858,29 +7768,28 @@
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr"/>
-      <c r="L83" s="3" t="inlineStr"/>
-      <c r="M83" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L83" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O83" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P83" s="3" t="inlineStr"/>
+      <c r="O83" s="3" t="inlineStr"/>
+      <c r="P83" s="3" t="inlineStr">
+        <is>
+          <t>200 {"ok":true,"ignored":"unknown_order"}</t>
+        </is>
+      </c>
       <c r="Q83" s="3" t="inlineStr">
-        <is>
-          <t>200 {"ok":true,"ignored":"unknown_order"}</t>
-        </is>
-      </c>
-      <c r="R83" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -7936,29 +7845,28 @@
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr"/>
-      <c r="L84" s="3" t="inlineStr"/>
-      <c r="M84" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L84" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O84" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P84" s="3" t="inlineStr"/>
+      <c r="O84" s="3" t="inlineStr"/>
+      <c r="P84" s="3" t="inlineStr">
+        <is>
+          <t>200 {"ok":true,"outcome":"CONFIRMED"} | DepositEvent=1 발행=1 status=COMPLETED</t>
+        </is>
+      </c>
       <c r="Q84" s="3" t="inlineStr">
-        <is>
-          <t>200 {"ok":true,"outcome":"CONFIRMED"} | DepositEvent=1 발행=1 status=COMPLETED</t>
-        </is>
-      </c>
-      <c r="R84" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -8014,29 +7922,28 @@
         </is>
       </c>
       <c r="K85" s="3" t="inlineStr"/>
-      <c r="L85" s="3" t="inlineStr"/>
-      <c r="M85" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L85" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N85" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O85" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P85" s="3" t="inlineStr"/>
+      <c r="O85" s="3" t="inlineStr"/>
+      <c r="P85" s="3" t="inlineStr">
+        <is>
+          <t>200 DepositEvent 1→1 발행 1→1 확정액 1000000→1000000 | 명세 18장 투자자 인수 테스트</t>
+        </is>
+      </c>
       <c r="Q85" s="3" t="inlineStr">
-        <is>
-          <t>200 DepositEvent 1→1 발행 1→1 확정액 1000000→1000000 | 명세 18장 투자자 인수 테스트</t>
-        </is>
-      </c>
-      <c r="R85" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -8092,29 +7999,28 @@
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr"/>
-      <c r="L86" s="3" t="inlineStr"/>
-      <c r="M86" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L86" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O86" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P86" s="3" t="inlineStr"/>
+      <c r="O86" s="3" t="inlineStr"/>
+      <c r="P86" s="3" t="inlineStr">
+        <is>
+          <t>codes=200,200,200 DepositEvent 1→1 발행 1→1 | confirmBankDeposit의 findUnique→create 사이 경합 확인</t>
+        </is>
+      </c>
       <c r="Q86" s="3" t="inlineStr">
-        <is>
-          <t>codes=200,200,200 DepositEvent 1→1 발행 1→1 | confirmBankDeposit의 findUnique→create 사이 경합 확인</t>
-        </is>
-      </c>
-      <c r="R86" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -8170,33 +8076,32 @@
         </is>
       </c>
       <c r="K87" s="3" t="inlineStr"/>
-      <c r="L87" s="3" t="inlineStr"/>
-      <c r="M87" s="14" t="inlineStr">
+      <c r="L87" s="14" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
       <c r="N87" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O87" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-001</t>
         </is>
       </c>
       <c r="P87" s="3" t="inlineStr">
         <is>
-          <t>REQ-001</t>
+          <t>200 {"ok":true,"outcome":"CONFIRMED"} | 발행 1→2</t>
         </is>
       </c>
       <c r="Q87" s="3" t="inlineStr">
-        <is>
-          <t>200 {"ok":true,"outcome":"CONFIRMED"} | 발행 1→2</t>
-        </is>
-      </c>
-      <c r="R87" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -8252,29 +8157,28 @@
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr"/>
-      <c r="L88" s="3" t="inlineStr"/>
-      <c r="M88" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L88" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O88" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P88" s="3" t="inlineStr"/>
+      <c r="O88" s="3" t="inlineStr"/>
+      <c r="P88" s="3" t="inlineStr">
+        <is>
+          <t>eligible=false status=IDENTITY_REQUIRED memo=남은 모집 물량보다 신청 금액이 큽니다.</t>
+        </is>
+      </c>
       <c r="Q88" s="3" t="inlineStr">
-        <is>
-          <t>eligible=false status=IDENTITY_REQUIRED memo=남은 모집 물량보다 신청 금액이 큽니다.</t>
-        </is>
-      </c>
-      <c r="R88" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -8330,29 +8234,28 @@
         </is>
       </c>
       <c r="K89" s="3" t="inlineStr"/>
-      <c r="L89" s="3" t="inlineStr"/>
-      <c r="M89" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L89" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N89" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O89" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P89" s="3" t="inlineStr"/>
+      <c r="O89" s="3" t="inlineStr"/>
+      <c r="P89" s="3" t="inlineStr">
+        <is>
+          <t>200 지점 2개 · 작물 0개 | 명세 B-01: 지점을 먼저 선택해야 다음 화면의 재고를 조회한다</t>
+        </is>
+      </c>
       <c r="Q89" s="3" t="inlineStr">
-        <is>
-          <t>200 지점 2개 · 작물 0개 | 명세 B-01: 지점을 먼저 선택해야 다음 화면의 재고를 조회한다</t>
-        </is>
-      </c>
-      <c r="R89" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -8408,29 +8311,28 @@
         </is>
       </c>
       <c r="K90" s="3" t="inlineStr"/>
-      <c r="L90" s="3" t="inlineStr"/>
-      <c r="M90" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L90" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N90" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O90" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P90" s="3" t="inlineStr"/>
+      <c r="O90" s="3" t="inlineStr"/>
+      <c r="P90" s="3" t="inlineStr">
+        <is>
+          <t>200 작물 3개 (구매가능 3개)</t>
+        </is>
+      </c>
       <c r="Q90" s="3" t="inlineStr">
-        <is>
-          <t>200 작물 3개 (구매가능 3개)</t>
-        </is>
-      </c>
-      <c r="R90" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -8486,29 +8388,28 @@
         </is>
       </c>
       <c r="K91" s="3" t="inlineStr"/>
-      <c r="L91" s="3" t="inlineStr"/>
-      <c r="M91" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L91" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N91" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O91" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P91" s="3" t="inlineStr"/>
+      <c r="O91" s="3" t="inlineStr"/>
+      <c r="P91" s="3" t="inlineStr">
+        <is>
+          <t>400 {"error":"작물 3종을 골라 주세요."}</t>
+        </is>
+      </c>
       <c r="Q91" s="3" t="inlineStr">
-        <is>
-          <t>400 {"error":"작물 3종을 골라 주세요."}</t>
-        </is>
-      </c>
-      <c r="R91" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -8564,29 +8465,28 @@
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr"/>
-      <c r="L92" s="3" t="inlineStr"/>
-      <c r="M92" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L92" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O92" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P92" s="3" t="inlineStr"/>
+      <c r="O92" s="3" t="inlineStr"/>
+      <c r="P92" s="3" t="inlineStr">
+        <is>
+          <t>400 {"error":"드레싱 2봉을 골라 주세요."}</t>
+        </is>
+      </c>
       <c r="Q92" s="3" t="inlineStr">
-        <is>
-          <t>400 {"error":"드레싱 2봉을 골라 주세요."}</t>
-        </is>
-      </c>
-      <c r="R92" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -8642,29 +8542,28 @@
         </is>
       </c>
       <c r="K93" s="3" t="inlineStr"/>
-      <c r="L93" s="3" t="inlineStr"/>
-      <c r="M93" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L93" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N93" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O93" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P93" s="3" t="inlineStr"/>
+      <c r="O93" s="3" t="inlineStr"/>
+      <c r="P93" s="3" t="inlineStr">
+        <is>
+          <t>400 {"error":"수령 주기를 골라 주세요."}</t>
+        </is>
+      </c>
       <c r="Q93" s="3" t="inlineStr">
-        <is>
-          <t>400 {"error":"수령 주기를 골라 주세요."}</t>
-        </is>
-      </c>
-      <c r="R93" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -8720,29 +8619,28 @@
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr"/>
-      <c r="L94" s="3" t="inlineStr"/>
-      <c r="M94" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L94" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O94" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P94" s="3" t="inlineStr"/>
+      <c r="O94" s="3" t="inlineStr"/>
+      <c r="P94" s="3" t="inlineStr">
+        <is>
+          <t>200 {"subscription":{"id":"cmt7gpkyb000604l99r27qoi9","userId":"cmt6qxua2000aesudro9pv9l9","projectId":"cmt6qxvrf000pesud96j1e56u","packSize":3,"perWeek":1,"productIds":["cmt6qxutw000lesud6hs7iq17","cmt6qxuv9000mesudwzrbh2ct","cmt6qxuwl000nesud</t>
+        </is>
+      </c>
       <c r="Q94" s="3" t="inlineStr">
-        <is>
-          <t>200 {"subscription":{"id":"cmt7gpkyb000604l99r27qoi9","userId":"cmt6qxua2000aesudro9pv9l9","projectId":"cmt6qxvrf000pesud96j1e56u","packSize":3,"perWeek":1,"productIds":["cmt6qxutw000lesud6hs7iq17","cmt6qxuv9000mesudwzrbh2ct","cmt6qxuwl000nesud</t>
-        </is>
-      </c>
-      <c r="R94" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -8798,29 +8696,28 @@
         </is>
       </c>
       <c r="K95" s="3" t="inlineStr"/>
-      <c r="L95" s="3" t="inlineStr"/>
-      <c r="M95" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L95" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N95" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O95" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P95" s="3" t="inlineStr"/>
+      <c r="O95" s="3" t="inlineStr"/>
+      <c r="P95" s="3" t="inlineStr">
+        <is>
+          <t>401 {"error":"Unauthorized"}</t>
+        </is>
+      </c>
       <c r="Q95" s="3" t="inlineStr">
-        <is>
-          <t>401 {"error":"Unauthorized"}</t>
-        </is>
-      </c>
-      <c r="R95" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -8876,33 +8773,32 @@
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr"/>
-      <c r="L96" s="3" t="inlineStr"/>
-      <c r="M96" s="14" t="inlineStr">
+      <c r="L96" s="14" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O96" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-002</t>
         </is>
       </c>
       <c r="P96" s="3" t="inlineStr">
         <is>
-          <t>REQ-002</t>
+          <t>200 {"success":true,"transaction":{"txHash":null,"amount":50000,"tokenAmount":5}} | 보유 1080→1085 | 명세 I-03: 동의 → AWAITING_DEPOSIT → 은행 웹훅 → 발행</t>
         </is>
       </c>
       <c r="Q96" s="3" t="inlineStr">
-        <is>
-          <t>200 {"success":true,"transaction":{"txHash":null,"amount":50000,"tokenAmount":5}} | 보유 1080→1085 | 명세 I-03: 동의 → AWAITING_DEPOSIT → 은행 웹훅 → 발행</t>
-        </is>
-      </c>
-      <c r="R96" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -8958,33 +8854,32 @@
         </is>
       </c>
       <c r="K97" s="3" t="inlineStr"/>
-      <c r="L97" s="3" t="inlineStr"/>
-      <c r="M97" s="14" t="inlineStr">
+      <c r="L97" s="14" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
       <c r="N97" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O97" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-006</t>
         </is>
       </c>
       <c r="P97" s="3" t="inlineStr">
         <is>
-          <t>REQ-006</t>
+          <t>가로 넘침: /(1010px), /projects(568px), /subscribe(546px), /about(627px)</t>
         </is>
       </c>
       <c r="Q97" s="3" t="inlineStr">
-        <is>
-          <t>가로 넘침: /(1010px), /projects(568px), /subscribe(546px), /about(627px)</t>
-        </is>
-      </c>
-      <c r="R97" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -9040,33 +8935,32 @@
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr"/>
-      <c r="L98" s="3" t="inlineStr"/>
-      <c r="M98" s="14" t="inlineStr">
+      <c r="L98" s="14" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+        </is>
+      </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O98" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-006</t>
         </is>
       </c>
       <c r="P98" s="3" t="inlineStr">
         <is>
-          <t>REQ-006</t>
+          <t>가로 넘침: /(1010px)</t>
         </is>
       </c>
       <c r="Q98" s="3" t="inlineStr">
-        <is>
-          <t>가로 넘침: /(1010px)</t>
-        </is>
-      </c>
-      <c r="R98" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -9122,29 +9016,28 @@
         </is>
       </c>
       <c r="K99" s="3" t="inlineStr"/>
-      <c r="L99" s="3" t="inlineStr"/>
-      <c r="M99" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L99" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N99" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O99" s="3" t="inlineStr">
-        <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="P99" s="3" t="inlineStr"/>
+      <c r="O99" s="3" t="inlineStr"/>
+      <c r="P99" s="3" t="inlineStr">
+        <is>
+          <t>검출 0건</t>
+        </is>
+      </c>
       <c r="Q99" s="3" t="inlineStr">
-        <is>
-          <t>검출 0건</t>
-        </is>
-      </c>
-      <c r="R99" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -9200,33 +9093,32 @@
         </is>
       </c>
       <c r="K100" s="3" t="inlineStr"/>
-      <c r="L100" s="3" t="inlineStr"/>
-      <c r="M100" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L100" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N100" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O100" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-005</t>
         </is>
       </c>
       <c r="P100" s="3" t="inlineStr">
         <is>
-          <t>REQ-005</t>
+          <t>401</t>
         </is>
       </c>
       <c r="Q100" s="3" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="R100" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -9282,33 +9174,32 @@
         </is>
       </c>
       <c r="K101" s="3" t="inlineStr"/>
-      <c r="L101" s="3" t="inlineStr"/>
-      <c r="M101" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L101" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N101" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O101" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-005</t>
         </is>
       </c>
       <c r="P101" s="3" t="inlineStr">
         <is>
-          <t>REQ-005</t>
+          <t>401</t>
         </is>
       </c>
       <c r="Q101" s="3" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="R101" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -9364,33 +9255,32 @@
         </is>
       </c>
       <c r="K102" s="3" t="inlineStr"/>
-      <c r="L102" s="3" t="inlineStr"/>
-      <c r="M102" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L102" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N102" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O102" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-005</t>
         </is>
       </c>
       <c r="P102" s="3" t="inlineStr">
         <is>
-          <t>REQ-005</t>
+          <t>403</t>
         </is>
       </c>
       <c r="Q102" s="3" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="R102" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -9446,33 +9336,32 @@
         </is>
       </c>
       <c r="K103" s="3" t="inlineStr"/>
-      <c r="L103" s="3" t="inlineStr"/>
-      <c r="M103" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L103" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N103" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O103" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-005</t>
         </is>
       </c>
       <c r="P103" s="3" t="inlineStr">
         <is>
-          <t>REQ-005</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Q103" s="3" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="R103" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -9528,33 +9417,32 @@
         </is>
       </c>
       <c r="K104" s="3" t="inlineStr"/>
-      <c r="L104" s="3" t="inlineStr"/>
-      <c r="M104" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L104" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O104" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-005</t>
         </is>
       </c>
       <c r="P104" s="3" t="inlineStr">
         <is>
-          <t>REQ-005</t>
+          <t>/login?next=/operator</t>
         </is>
       </c>
       <c r="Q104" s="3" t="inlineStr">
-        <is>
-          <t>/login?next=/operator</t>
-        </is>
-      </c>
-      <c r="R104" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -9610,33 +9498,32 @@
         </is>
       </c>
       <c r="K105" s="3" t="inlineStr"/>
-      <c r="L105" s="3" t="inlineStr"/>
-      <c r="M105" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L105" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N105" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O105" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-005</t>
         </is>
       </c>
       <c r="P105" s="3" t="inlineStr">
         <is>
-          <t>REQ-005</t>
+          <t>/investor</t>
         </is>
       </c>
       <c r="Q105" s="3" t="inlineStr">
-        <is>
-          <t>/investor</t>
-        </is>
-      </c>
-      <c r="R105" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -9692,33 +9579,32 @@
         </is>
       </c>
       <c r="K106" s="3" t="inlineStr"/>
-      <c r="L106" s="3" t="inlineStr"/>
-      <c r="M106" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L106" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O106" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-004</t>
         </is>
       </c>
       <c r="P106" s="3" t="inlineStr">
         <is>
-          <t>REQ-004</t>
+          <t>/investor</t>
         </is>
       </c>
       <c r="Q106" s="3" t="inlineStr">
-        <is>
-          <t>/investor</t>
-        </is>
-      </c>
-      <c r="R106" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -9774,33 +9660,32 @@
         </is>
       </c>
       <c r="K107" s="3" t="inlineStr"/>
-      <c r="L107" s="3" t="inlineStr"/>
-      <c r="M107" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L107" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N107" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O107" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-004</t>
         </is>
       </c>
       <c r="P107" s="3" t="inlineStr">
         <is>
-          <t>REQ-004</t>
+          <t>/investor</t>
         </is>
       </c>
       <c r="Q107" s="3" t="inlineStr">
-        <is>
-          <t>/investor</t>
-        </is>
-      </c>
-      <c r="R107" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -9856,33 +9741,32 @@
         </is>
       </c>
       <c r="K108" s="3" t="inlineStr"/>
-      <c r="L108" s="3" t="inlineStr"/>
-      <c r="M108" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L108" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O108" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-004</t>
         </is>
       </c>
       <c r="P108" s="3" t="inlineStr">
         <is>
-          <t>REQ-004</t>
+          <t>/investor</t>
         </is>
       </c>
       <c r="Q108" s="3" t="inlineStr">
-        <is>
-          <t>/investor</t>
-        </is>
-      </c>
-      <c r="R108" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -9938,33 +9822,32 @@
         </is>
       </c>
       <c r="K109" s="3" t="inlineStr"/>
-      <c r="L109" s="3" t="inlineStr"/>
-      <c r="M109" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L109" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N109" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O109" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-004</t>
         </is>
       </c>
       <c r="P109" s="3" t="inlineStr">
         <is>
-          <t>REQ-004</t>
+          <t>/investor</t>
         </is>
       </c>
       <c r="Q109" s="3" t="inlineStr">
-        <is>
-          <t>/investor</t>
-        </is>
-      </c>
-      <c r="R109" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -10020,33 +9903,32 @@
         </is>
       </c>
       <c r="K110" s="3" t="inlineStr"/>
-      <c r="L110" s="3" t="inlineStr"/>
-      <c r="M110" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L110" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O110" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-004</t>
         </is>
       </c>
       <c r="P110" s="3" t="inlineStr">
         <is>
-          <t>REQ-004</t>
+          <t>/admin</t>
         </is>
       </c>
       <c r="Q110" s="3" t="inlineStr">
-        <is>
-          <t>/admin</t>
-        </is>
-      </c>
-      <c r="R110" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -10102,33 +9984,32 @@
         </is>
       </c>
       <c r="K111" s="3" t="inlineStr"/>
-      <c r="L111" s="3" t="inlineStr"/>
-      <c r="M111" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L111" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N111" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O111" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-004</t>
         </is>
       </c>
       <c r="P111" s="3" t="inlineStr">
         <is>
-          <t>REQ-004</t>
+          <t>/operator/milestones</t>
         </is>
       </c>
       <c r="Q111" s="3" t="inlineStr">
-        <is>
-          <t>/operator/milestones</t>
-        </is>
-      </c>
-      <c r="R111" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -10184,33 +10065,32 @@
         </is>
       </c>
       <c r="K112" s="3" t="inlineStr"/>
-      <c r="L112" s="3" t="inlineStr"/>
-      <c r="M112" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L112" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O112" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-002</t>
         </is>
       </c>
       <c r="P112" s="3" t="inlineStr">
         <is>
-          <t>REQ-002</t>
+          <t>404</t>
         </is>
       </c>
       <c r="Q112" s="3" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="R112" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -10266,33 +10146,32 @@
         </is>
       </c>
       <c r="K113" s="3" t="inlineStr"/>
-      <c r="L113" s="3" t="inlineStr"/>
-      <c r="M113" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L113" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N113" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O113" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-003</t>
         </is>
       </c>
       <c r="P113" s="3" t="inlineStr">
         <is>
-          <t>REQ-003</t>
+          <t>403 배정된 지점의 운영자만 제출할 수 있습니다</t>
         </is>
       </c>
       <c r="Q113" s="3" t="inlineStr">
-        <is>
-          <t>403 배정된 지점의 운영자만 제출할 수 있습니다</t>
-        </is>
-      </c>
-      <c r="R113" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -10348,33 +10227,32 @@
         </is>
       </c>
       <c r="K114" s="3" t="inlineStr"/>
-      <c r="L114" s="3" t="inlineStr"/>
-      <c r="M114" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L114" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O114" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-003</t>
         </is>
       </c>
       <c r="P114" s="3" t="inlineStr">
         <is>
-          <t>REQ-003</t>
+          <t>403</t>
         </is>
       </c>
       <c r="Q114" s="3" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="R114" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -10430,33 +10308,32 @@
         </is>
       </c>
       <c r="K115" s="3" t="inlineStr"/>
-      <c r="L115" s="3" t="inlineStr"/>
-      <c r="M115" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L115" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N115" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O115" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-003</t>
         </is>
       </c>
       <c r="P115" s="3" t="inlineStr">
         <is>
-          <t>REQ-003</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Q115" s="3" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="R115" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -10512,33 +10389,32 @@
         </is>
       </c>
       <c r="K116" s="3" t="inlineStr"/>
-      <c r="L116" s="3" t="inlineStr"/>
-      <c r="M116" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L116" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N116" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O116" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-001</t>
         </is>
       </c>
       <c r="P116" s="3" t="inlineStr">
         <is>
-          <t>REQ-001</t>
+          <t>CONFIRMED · de=1 · 청약 COMPLETED</t>
         </is>
       </c>
       <c r="Q116" s="3" t="inlineStr">
-        <is>
-          <t>CONFIRMED · de=1 · 청약 COMPLETED</t>
-        </is>
-      </c>
-      <c r="R116" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -10594,33 +10470,32 @@
         </is>
       </c>
       <c r="K117" s="3" t="inlineStr"/>
-      <c r="L117" s="3" t="inlineStr"/>
-      <c r="M117" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L117" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N117" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O117" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-001</t>
         </is>
       </c>
       <c r="P117" s="3" t="inlineStr">
         <is>
-          <t>REQ-001</t>
+          <t>DUPLICATE · 불변</t>
         </is>
       </c>
       <c r="Q117" s="3" t="inlineStr">
-        <is>
-          <t>DUPLICATE · 불변</t>
-        </is>
-      </c>
-      <c r="R117" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -10676,33 +10551,32 @@
         </is>
       </c>
       <c r="K118" s="3" t="inlineStr"/>
-      <c r="L118" s="3" t="inlineStr"/>
-      <c r="M118" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L118" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N118" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O118" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-001</t>
         </is>
       </c>
       <c r="P118" s="3" t="inlineStr">
         <is>
-          <t>REQ-001</t>
+          <t>REVIEW · 발행 불변 · 모집 3580→3580</t>
         </is>
       </c>
       <c r="Q118" s="3" t="inlineStr">
-        <is>
-          <t>REVIEW · 발행 불변 · 모집 3580→3580</t>
-        </is>
-      </c>
-      <c r="R118" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -10758,33 +10632,32 @@
         </is>
       </c>
       <c r="K119" s="3" t="inlineStr"/>
-      <c r="L119" s="3" t="inlineStr"/>
-      <c r="M119" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L119" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N119" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O119" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-001</t>
         </is>
       </c>
       <c r="P119" s="3" t="inlineStr">
         <is>
-          <t>REQ-001</t>
+          <t>포함됨</t>
         </is>
       </c>
       <c r="Q119" s="3" t="inlineStr">
-        <is>
-          <t>포함됨</t>
-        </is>
-      </c>
-      <c r="R119" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -10840,33 +10713,32 @@
         </is>
       </c>
       <c r="K120" s="3" t="inlineStr"/>
-      <c r="L120" s="3" t="inlineStr"/>
-      <c r="M120" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L120" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N120" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O120" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-007</t>
         </is>
       </c>
       <c r="P120" s="3" t="inlineStr">
         <is>
-          <t>REQ-007</t>
+          <t>링크 없음 · 404 없음</t>
         </is>
       </c>
       <c r="Q120" s="3" t="inlineStr">
-        <is>
-          <t>링크 없음 · 404 없음</t>
-        </is>
-      </c>
-      <c r="R120" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -10922,33 +10794,32 @@
         </is>
       </c>
       <c r="K121" s="3" t="inlineStr"/>
-      <c r="L121" s="3" t="inlineStr"/>
-      <c r="M121" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L121" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N121" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O121" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-006</t>
         </is>
       </c>
       <c r="P121" s="3" t="inlineStr">
         <is>
-          <t>REQ-006</t>
+          <t>넘침 없음</t>
         </is>
       </c>
       <c r="Q121" s="3" t="inlineStr">
-        <is>
-          <t>넘침 없음</t>
-        </is>
-      </c>
-      <c r="R121" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -11004,33 +10875,32 @@
         </is>
       </c>
       <c r="K122" s="3" t="inlineStr"/>
-      <c r="L122" s="3" t="inlineStr"/>
-      <c r="M122" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L122" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N122" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O122" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>REQ-006</t>
         </is>
       </c>
       <c r="P122" s="3" t="inlineStr">
         <is>
-          <t>REQ-006</t>
+          <t>넘침 없음</t>
         </is>
       </c>
       <c r="Q122" s="3" t="inlineStr">
-        <is>
-          <t>넘침 없음</t>
-        </is>
-      </c>
-      <c r="R122" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -11086,33 +10956,32 @@
         </is>
       </c>
       <c r="K123" s="3" t="inlineStr"/>
-      <c r="L123" s="3" t="inlineStr"/>
-      <c r="M123" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L123" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N123" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O123" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>요청 1</t>
         </is>
       </c>
       <c r="P123" s="3" t="inlineStr">
         <is>
-          <t>요청 1</t>
+          <t>비보장 미검출 · 목표 배지 유지</t>
         </is>
       </c>
       <c r="Q123" s="3" t="inlineStr">
-        <is>
-          <t>비보장 미검출 · 목표 배지 유지</t>
-        </is>
-      </c>
-      <c r="R123" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -11168,33 +11037,32 @@
         </is>
       </c>
       <c r="K124" s="3" t="inlineStr"/>
-      <c r="L124" s="3" t="inlineStr"/>
-      <c r="M124" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L124" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N124" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O124" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>요청 2</t>
         </is>
       </c>
       <c r="P124" s="3" t="inlineStr">
         <is>
-          <t>요청 2</t>
+          <t>오버레이 노출 · 카드 3장 · 이동 없음</t>
         </is>
       </c>
       <c r="Q124" s="3" t="inlineStr">
-        <is>
-          <t>오버레이 노출 · 카드 3장 · 이동 없음</t>
-        </is>
-      </c>
-      <c r="R124" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -11250,33 +11118,32 @@
         </is>
       </c>
       <c r="K125" s="3" t="inlineStr"/>
-      <c r="L125" s="3" t="inlineStr"/>
-      <c r="M125" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L125" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N125" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O125" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>요청 2</t>
         </is>
       </c>
       <c r="P125" s="3" t="inlineStr">
         <is>
-          <t>요청 2</t>
+          <t>오버레이 없음 · /projects/[id] 이동</t>
         </is>
       </c>
       <c r="Q125" s="3" t="inlineStr">
-        <is>
-          <t>오버레이 없음 · /projects/[id] 이동</t>
-        </is>
-      </c>
-      <c r="R125" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -11332,33 +11199,32 @@
         </is>
       </c>
       <c r="K126" s="3" t="inlineStr"/>
-      <c r="L126" s="3" t="inlineStr"/>
-      <c r="M126" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L126" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N126" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O126" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>요청 3</t>
         </is>
       </c>
       <c r="P126" s="3" t="inlineStr">
         <is>
-          <t>요청 3</t>
+          <t>4개 모두 노출 · 옛 문구 4개 모두 제거</t>
         </is>
       </c>
       <c r="Q126" s="3" t="inlineStr">
-        <is>
-          <t>4개 모두 노출 · 옛 문구 4개 모두 제거</t>
-        </is>
-      </c>
-      <c r="R126" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -11414,33 +11280,32 @@
         </is>
       </c>
       <c r="K127" s="3" t="inlineStr"/>
-      <c r="L127" s="3" t="inlineStr"/>
-      <c r="M127" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L127" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N127" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O127" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>요청 4</t>
         </is>
       </c>
       <c r="P127" s="3" t="inlineStr">
         <is>
-          <t>요청 4</t>
+          <t>노출됨</t>
         </is>
       </c>
       <c r="Q127" s="3" t="inlineStr">
-        <is>
-          <t>노출됨</t>
-        </is>
-      </c>
-      <c r="R127" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -11496,33 +11361,32 @@
         </is>
       </c>
       <c r="K128" s="3" t="inlineStr"/>
-      <c r="L128" s="3" t="inlineStr"/>
-      <c r="M128" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L128" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N128" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O128" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>요청 4</t>
         </is>
       </c>
       <c r="P128" s="3" t="inlineStr">
         <is>
-          <t>요청 4</t>
+          <t>금액 보존 확인</t>
         </is>
       </c>
       <c r="Q128" s="3" t="inlineStr">
-        <is>
-          <t>금액 보존 확인</t>
-        </is>
-      </c>
-      <c r="R128" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -11578,33 +11442,32 @@
         </is>
       </c>
       <c r="K129" s="3" t="inlineStr"/>
-      <c r="L129" s="3" t="inlineStr"/>
-      <c r="M129" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L129" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N129" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O129" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>요청 4</t>
         </is>
       </c>
       <c r="P129" s="3" t="inlineStr">
         <is>
-          <t>요청 4</t>
+          <t>next 유지 확인</t>
         </is>
       </c>
       <c r="Q129" s="3" t="inlineStr">
-        <is>
-          <t>next 유지 확인</t>
-        </is>
-      </c>
-      <c r="R129" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -11660,33 +11523,32 @@
         </is>
       </c>
       <c r="K130" s="3" t="inlineStr"/>
-      <c r="L130" s="3" t="inlineStr"/>
-      <c r="M130" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L130" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N130" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O130" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>요청 5</t>
         </is>
       </c>
       <c r="P130" s="3" t="inlineStr">
         <is>
-          <t>요청 5</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="Q130" s="3" t="inlineStr">
-        <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="R130" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -11742,33 +11604,32 @@
         </is>
       </c>
       <c r="K131" s="3" t="inlineStr"/>
-      <c r="L131" s="3" t="inlineStr"/>
-      <c r="M131" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L131" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N131" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O131" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>요청 5</t>
         </is>
       </c>
       <c r="P131" s="3" t="inlineStr">
         <is>
-          <t>요청 5</t>
+          <t>…/invest/eligibility?amount=100000</t>
         </is>
       </c>
       <c r="Q131" s="3" t="inlineStr">
-        <is>
-          <t>…/invest/eligibility?amount=100000</t>
-        </is>
-      </c>
-      <c r="R131" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -11824,33 +11685,32 @@
         </is>
       </c>
       <c r="K132" s="3" t="inlineStr"/>
-      <c r="L132" s="3" t="inlineStr"/>
-      <c r="M132" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L132" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N132" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="O132" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>요청 5</t>
         </is>
       </c>
       <c r="P132" s="3" t="inlineStr">
         <is>
-          <t>요청 5</t>
+          <t>1건 등록됨</t>
         </is>
       </c>
       <c r="Q132" s="3" t="inlineStr">
-        <is>
-          <t>1건 등록됨</t>
-        </is>
-      </c>
-      <c r="R132" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -11906,37 +11766,32 @@
         </is>
       </c>
       <c r="K133" s="3" t="n"/>
-      <c r="L133" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M133" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L133" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N133" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O133" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>REQ-005</t>
         </is>
       </c>
       <c r="P133" s="3" t="inlineStr">
         <is>
-          <t>REQ-005</t>
+          <t>401</t>
         </is>
       </c>
       <c r="Q133" s="3" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="R133" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -11992,37 +11847,32 @@
         </is>
       </c>
       <c r="K134" s="3" t="n"/>
-      <c r="L134" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M134" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L134" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N134" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O134" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>REQ-005</t>
         </is>
       </c>
       <c r="P134" s="3" t="inlineStr">
         <is>
-          <t>REQ-005</t>
+          <t>401</t>
         </is>
       </c>
       <c r="Q134" s="3" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="R134" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -12078,37 +11928,32 @@
         </is>
       </c>
       <c r="K135" s="3" t="n"/>
-      <c r="L135" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M135" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L135" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N135" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O135" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>REQ-005</t>
         </is>
       </c>
       <c r="P135" s="3" t="inlineStr">
         <is>
-          <t>REQ-005</t>
+          <t>403</t>
         </is>
       </c>
       <c r="Q135" s="3" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="R135" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -12164,37 +12009,32 @@
         </is>
       </c>
       <c r="K136" s="3" t="n"/>
-      <c r="L136" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M136" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L136" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N136" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O136" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>REQ-005</t>
         </is>
       </c>
       <c r="P136" s="3" t="inlineStr">
         <is>
-          <t>REQ-005</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Q136" s="3" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="R136" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -12250,37 +12090,32 @@
         </is>
       </c>
       <c r="K137" s="3" t="n"/>
-      <c r="L137" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M137" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L137" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N137" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O137" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>REQ-005</t>
         </is>
       </c>
       <c r="P137" s="3" t="inlineStr">
         <is>
-          <t>REQ-005</t>
+          <t>/login?next=/operator</t>
         </is>
       </c>
       <c r="Q137" s="3" t="inlineStr">
-        <is>
-          <t>/login?next=/operator</t>
-        </is>
-      </c>
-      <c r="R137" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -12336,37 +12171,32 @@
         </is>
       </c>
       <c r="K138" s="3" t="n"/>
-      <c r="L138" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M138" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L138" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N138" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O138" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>REQ-005</t>
         </is>
       </c>
       <c r="P138" s="3" t="inlineStr">
         <is>
-          <t>REQ-005</t>
+          <t>/investor</t>
         </is>
       </c>
       <c r="Q138" s="3" t="inlineStr">
-        <is>
-          <t>/investor</t>
-        </is>
-      </c>
-      <c r="R138" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -12422,37 +12252,32 @@
         </is>
       </c>
       <c r="K139" s="3" t="n"/>
-      <c r="L139" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M139" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L139" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N139" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O139" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>REQ-004</t>
         </is>
       </c>
       <c r="P139" s="3" t="inlineStr">
         <is>
-          <t>REQ-004</t>
+          <t>/investor</t>
         </is>
       </c>
       <c r="Q139" s="3" t="inlineStr">
-        <is>
-          <t>/investor</t>
-        </is>
-      </c>
-      <c r="R139" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -12508,37 +12333,32 @@
         </is>
       </c>
       <c r="K140" s="3" t="n"/>
-      <c r="L140" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M140" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L140" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N140" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O140" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>REQ-004</t>
         </is>
       </c>
       <c r="P140" s="3" t="inlineStr">
         <is>
-          <t>REQ-004</t>
+          <t>/investor</t>
         </is>
       </c>
       <c r="Q140" s="3" t="inlineStr">
-        <is>
-          <t>/investor</t>
-        </is>
-      </c>
-      <c r="R140" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -12594,37 +12414,32 @@
         </is>
       </c>
       <c r="K141" s="3" t="n"/>
-      <c r="L141" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M141" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L141" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N141" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O141" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>REQ-004</t>
         </is>
       </c>
       <c r="P141" s="3" t="inlineStr">
         <is>
-          <t>REQ-004</t>
+          <t>/investor</t>
         </is>
       </c>
       <c r="Q141" s="3" t="inlineStr">
-        <is>
-          <t>/investor</t>
-        </is>
-      </c>
-      <c r="R141" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -12680,37 +12495,32 @@
         </is>
       </c>
       <c r="K142" s="3" t="n"/>
-      <c r="L142" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M142" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L142" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N142" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O142" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>REQ-004</t>
         </is>
       </c>
       <c r="P142" s="3" t="inlineStr">
         <is>
-          <t>REQ-004</t>
+          <t>/investor</t>
         </is>
       </c>
       <c r="Q142" s="3" t="inlineStr">
-        <is>
-          <t>/investor</t>
-        </is>
-      </c>
-      <c r="R142" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -12766,37 +12576,32 @@
         </is>
       </c>
       <c r="K143" s="3" t="n"/>
-      <c r="L143" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M143" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L143" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N143" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O143" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>REQ-004</t>
         </is>
       </c>
       <c r="P143" s="3" t="inlineStr">
         <is>
-          <t>REQ-004</t>
+          <t>/admin</t>
         </is>
       </c>
       <c r="Q143" s="3" t="inlineStr">
-        <is>
-          <t>/admin</t>
-        </is>
-      </c>
-      <c r="R143" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -12852,37 +12657,32 @@
         </is>
       </c>
       <c r="K144" s="3" t="n"/>
-      <c r="L144" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M144" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L144" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N144" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O144" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>REQ-004</t>
         </is>
       </c>
       <c r="P144" s="3" t="inlineStr">
         <is>
-          <t>REQ-004</t>
+          <t>/operator/milestones</t>
         </is>
       </c>
       <c r="Q144" s="3" t="inlineStr">
-        <is>
-          <t>/operator/milestones</t>
-        </is>
-      </c>
-      <c r="R144" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -12938,37 +12738,32 @@
         </is>
       </c>
       <c r="K145" s="3" t="n"/>
-      <c r="L145" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M145" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L145" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N145" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O145" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>REQ-002</t>
         </is>
       </c>
       <c r="P145" s="3" t="inlineStr">
         <is>
-          <t>REQ-002</t>
+          <t>404</t>
         </is>
       </c>
       <c r="Q145" s="3" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="R145" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -13024,37 +12819,32 @@
         </is>
       </c>
       <c r="K146" s="3" t="n"/>
-      <c r="L146" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M146" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L146" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N146" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O146" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>REQ-003</t>
         </is>
       </c>
       <c r="P146" s="3" t="inlineStr">
         <is>
-          <t>REQ-003</t>
+          <t>403 배정된 지점의 운영자만 제출할 수 있습니다</t>
         </is>
       </c>
       <c r="Q146" s="3" t="inlineStr">
-        <is>
-          <t>403 배정된 지점의 운영자만 제출할 수 있습니다</t>
-        </is>
-      </c>
-      <c r="R146" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -13110,37 +12900,32 @@
         </is>
       </c>
       <c r="K147" s="3" t="n"/>
-      <c r="L147" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M147" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L147" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N147" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O147" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>REQ-003</t>
         </is>
       </c>
       <c r="P147" s="3" t="inlineStr">
         <is>
-          <t>REQ-003</t>
+          <t>403 배정된 지점의 운영자만 제출할 수 있습니다</t>
         </is>
       </c>
       <c r="Q147" s="3" t="inlineStr">
-        <is>
-          <t>403 배정된 지점의 운영자만 제출할 수 있습니다</t>
-        </is>
-      </c>
-      <c r="R147" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -13196,37 +12981,32 @@
         </is>
       </c>
       <c r="K148" s="3" t="n"/>
-      <c r="L148" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M148" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L148" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N148" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O148" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>REQ-003</t>
         </is>
       </c>
       <c r="P148" s="3" t="inlineStr">
         <is>
-          <t>REQ-003</t>
+          <t>200 · evidence_submitted</t>
         </is>
       </c>
       <c r="Q148" s="3" t="inlineStr">
-        <is>
-          <t>200 · evidence_submitted</t>
-        </is>
-      </c>
-      <c r="R148" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -13282,37 +13062,32 @@
         </is>
       </c>
       <c r="K149" s="3" t="n"/>
-      <c r="L149" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M149" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L149" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N149" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O149" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>REQ-001</t>
         </is>
       </c>
       <c r="P149" s="3" t="inlineStr">
         <is>
-          <t>REQ-001</t>
+          <t>CONFIRMED · DepositEvent 1건 · 청약 COMPLETED</t>
         </is>
       </c>
       <c r="Q149" s="3" t="inlineStr">
-        <is>
-          <t>CONFIRMED · DepositEvent 1건 · 청약 COMPLETED</t>
-        </is>
-      </c>
-      <c r="R149" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -13368,37 +13143,32 @@
         </is>
       </c>
       <c r="K150" s="3" t="n"/>
-      <c r="L150" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M150" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L150" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N150" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O150" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>REQ-001</t>
         </is>
       </c>
       <c r="P150" s="3" t="inlineStr">
         <is>
-          <t>REQ-001</t>
+          <t>DUPLICATE · 건수 불변(1건)</t>
         </is>
       </c>
       <c r="Q150" s="3" t="inlineStr">
-        <is>
-          <t>DUPLICATE · 건수 불변(1건)</t>
-        </is>
-      </c>
-      <c r="R150" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -13454,37 +13224,32 @@
         </is>
       </c>
       <c r="K151" s="3" t="n"/>
-      <c r="L151" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M151" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L151" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N151" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O151" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>REQ-001</t>
         </is>
       </c>
       <c r="P151" s="3" t="inlineStr">
         <is>
-          <t>REQ-001</t>
+          <t>REVIEW · 발행 1건 그대로 · 모집액에 1차분만 반영</t>
         </is>
       </c>
       <c r="Q151" s="3" t="inlineStr">
-        <is>
-          <t>REVIEW · 발행 1건 그대로 · 모집액에 1차분만 반영</t>
-        </is>
-      </c>
-      <c r="R151" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -13540,37 +13305,32 @@
         </is>
       </c>
       <c r="K152" s="3" t="n"/>
-      <c r="L152" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M152" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L152" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N152" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O152" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>REQ-001</t>
         </is>
       </c>
       <c r="P152" s="3" t="inlineStr">
         <is>
-          <t>REQ-001</t>
+          <t>검토 큐에 포함됨</t>
         </is>
       </c>
       <c r="Q152" s="3" t="inlineStr">
-        <is>
-          <t>검토 큐에 포함됨</t>
-        </is>
-      </c>
-      <c r="R152" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -13626,37 +13386,32 @@
         </is>
       </c>
       <c r="K153" s="3" t="n"/>
-      <c r="L153" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M153" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L153" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N153" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O153" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>REQ-007</t>
         </is>
       </c>
       <c r="P153" s="3" t="inlineStr">
         <is>
-          <t>REQ-007</t>
+          <t>/investor/payouts 링크 0건 · 404 응답 0건</t>
         </is>
       </c>
       <c r="Q153" s="3" t="inlineStr">
-        <is>
-          <t>/investor/payouts 링크 0건 · 404 응답 0건</t>
-        </is>
-      </c>
-      <c r="R153" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -13712,37 +13467,32 @@
         </is>
       </c>
       <c r="K154" s="3" t="n"/>
-      <c r="L154" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M154" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L154" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N154" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O154" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>REQ-006</t>
         </is>
       </c>
       <c r="P154" s="3" t="inlineStr">
         <is>
-          <t>REQ-006</t>
+          <t>주요 5화면 모두 390px 이내</t>
         </is>
       </c>
       <c r="Q154" s="3" t="inlineStr">
-        <is>
-          <t>주요 5화면 모두 390px 이내</t>
-        </is>
-      </c>
-      <c r="R154" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -13798,37 +13548,32 @@
         </is>
       </c>
       <c r="K155" s="3" t="n"/>
-      <c r="L155" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M155" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L155" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N155" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O155" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>REQ-006</t>
         </is>
       </c>
       <c r="P155" s="3" t="inlineStr">
         <is>
-          <t>REQ-006</t>
+          <t>주요 5화면 모두 768px 이내</t>
         </is>
       </c>
       <c r="Q155" s="3" t="inlineStr">
-        <is>
-          <t>주요 5화면 모두 768px 이내</t>
-        </is>
-      </c>
-      <c r="R155" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -13884,37 +13629,32 @@
         </is>
       </c>
       <c r="K156" s="3" t="n"/>
-      <c r="L156" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M156" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L156" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N156" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O156" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>요청 1</t>
         </is>
       </c>
       <c r="P156" s="3" t="inlineStr">
         <is>
-          <t>요청 1</t>
+          <t>비보장 미검출 · 목표 배지 유지</t>
         </is>
       </c>
       <c r="Q156" s="3" t="inlineStr">
-        <is>
-          <t>비보장 미검출 · 목표 배지 유지</t>
-        </is>
-      </c>
-      <c r="R156" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -13970,37 +13710,32 @@
         </is>
       </c>
       <c r="K157" s="3" t="n"/>
-      <c r="L157" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M157" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L157" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N157" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O157" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>요청 2</t>
         </is>
       </c>
       <c r="P157" s="3" t="inlineStr">
         <is>
-          <t>요청 2</t>
+          <t>오버레이 노출 · 로그인 버튼 2개 · 카드 클릭해도 이동 없음</t>
         </is>
       </c>
       <c r="Q157" s="3" t="inlineStr">
-        <is>
-          <t>오버레이 노출 · 로그인 버튼 2개 · 카드 클릭해도 이동 없음</t>
-        </is>
-      </c>
-      <c r="R157" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -14056,37 +13791,32 @@
         </is>
       </c>
       <c r="K158" s="3" t="n"/>
-      <c r="L158" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M158" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L158" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O158" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>요청 2</t>
         </is>
       </c>
       <c r="P158" s="3" t="inlineStr">
         <is>
-          <t>요청 2</t>
+          <t>오버레이 없음 · /projects/[id] 이동</t>
         </is>
       </c>
       <c r="Q158" s="3" t="inlineStr">
-        <is>
-          <t>오버레이 없음 · /projects/[id] 이동</t>
-        </is>
-      </c>
-      <c r="R158" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -14142,37 +13872,32 @@
         </is>
       </c>
       <c r="K159" s="3" t="n"/>
-      <c r="L159" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M159" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L159" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N159" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O159" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>요청 3</t>
         </is>
       </c>
       <c r="P159" s="3" t="inlineStr">
         <is>
-          <t>요청 3</t>
+          <t>새 문구 4개 노출 · 옛 문구 4개 미검출</t>
         </is>
       </c>
       <c r="Q159" s="3" t="inlineStr">
-        <is>
-          <t>새 문구 4개 노출 · 옛 문구 4개 미검출</t>
-        </is>
-      </c>
-      <c r="R159" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -14228,37 +13953,32 @@
         </is>
       </c>
       <c r="K160" s="3" t="n"/>
-      <c r="L160" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M160" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L160" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N160" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O160" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>요청 4</t>
         </is>
       </c>
       <c r="P160" s="3" t="inlineStr">
         <is>
-          <t>요청 4</t>
+          <t>본인확인하고 신청하기</t>
         </is>
       </c>
       <c r="Q160" s="3" t="inlineStr">
-        <is>
-          <t>본인확인하고 신청하기</t>
-        </is>
-      </c>
-      <c r="R160" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -14314,37 +14034,32 @@
         </is>
       </c>
       <c r="K161" s="3" t="n"/>
-      <c r="L161" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M161" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L161" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N161" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O161" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>요청 4</t>
         </is>
       </c>
       <c r="P161" s="3" t="inlineStr">
         <is>
-          <t>요청 4</t>
+          <t>/verify?next=/projects/[id]/invest/eligibility?amount=100000</t>
         </is>
       </c>
       <c r="Q161" s="3" t="inlineStr">
-        <is>
-          <t>/verify?next=/projects/[id]/invest/eligibility?amount=100000</t>
-        </is>
-      </c>
-      <c r="R161" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -14400,37 +14115,32 @@
         </is>
       </c>
       <c r="K162" s="3" t="n"/>
-      <c r="L162" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M162" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L162" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N162" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O162" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>요청 4</t>
         </is>
       </c>
       <c r="P162" s="3" t="inlineStr">
         <is>
-          <t>요청 4</t>
+          <t>/verify/mobile-id?next=…amount=100000</t>
         </is>
       </c>
       <c r="Q162" s="3" t="inlineStr">
-        <is>
-          <t>/verify/mobile-id?next=…amount=100000</t>
-        </is>
-      </c>
-      <c r="R162" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -14486,37 +14196,32 @@
         </is>
       </c>
       <c r="K163" s="3" t="n"/>
-      <c r="L163" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M163" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L163" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N163" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O163" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>요청 5</t>
         </is>
       </c>
       <c r="P163" s="3" t="inlineStr">
         <is>
-          <t>요청 5</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="Q163" s="3" t="inlineStr">
-        <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="R163" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -14572,37 +14277,32 @@
         </is>
       </c>
       <c r="K164" s="3" t="n"/>
-      <c r="L164" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M164" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L164" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N164" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O164" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>요청 5</t>
         </is>
       </c>
       <c r="P164" s="3" t="inlineStr">
         <is>
-          <t>요청 5</t>
+          <t>/projects/[id]/invest/eligibility?amount=100000</t>
         </is>
       </c>
       <c r="Q164" s="3" t="inlineStr">
-        <is>
-          <t>/projects/[id]/invest/eligibility?amount=100000</t>
-        </is>
-      </c>
-      <c r="R164" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -14658,37 +14358,32 @@
         </is>
       </c>
       <c r="K165" s="3" t="n"/>
-      <c r="L165" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M165" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L165" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N165" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O165" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>요청 5</t>
         </is>
       </c>
       <c r="P165" s="3" t="inlineStr">
         <is>
-          <t>요청 5</t>
+          <t>1건 등록됨</t>
         </is>
       </c>
       <c r="Q165" s="3" t="inlineStr">
-        <is>
-          <t>1건 등록됨</t>
-        </is>
-      </c>
-      <c r="R165" s="3" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
@@ -14748,33 +14443,28 @@
           <t>서버 로직</t>
         </is>
       </c>
-      <c r="L166" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M166" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L166" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N166" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O166" s="3" t="inlineStr">
-        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="P166" s="3" t="inlineStr"/>
+      <c r="O166" s="3" t="inlineStr"/>
+      <c r="P166" s="3" t="inlineStr">
+        <is>
+          <t>QR 1건 노출 · 실패 문구 0건 · /api/identity/offer 200</t>
+        </is>
+      </c>
       <c r="Q166" s="3" t="inlineStr">
-        <is>
-          <t>QR 1건 노출 · 실패 문구 0건 · /api/identity/offer 200</t>
-        </is>
-      </c>
-      <c r="R166" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -14834,37 +14524,32 @@
           <t>서버 로직</t>
         </is>
       </c>
-      <c r="L167" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M167" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L167" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>API 직접 호출 (프로덕션)</t>
         </is>
       </c>
       <c r="N167" s="3" t="inlineStr">
         <is>
-          <t>API 직접 호출 (프로덕션)</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="O167" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>REQ-008</t>
         </is>
       </c>
       <c r="P167" s="3" t="inlineStr">
         <is>
-          <t>REQ-008</t>
+          <t>실계정 tj041600@naver.com 보존 · 본인확인 5/5 · 전체 유저 8</t>
         </is>
       </c>
       <c r="Q167" s="3" t="inlineStr">
-        <is>
-          <t>실계정 tj041600@naver.com 보존 · 본인확인 5/5 · 전체 유저 8</t>
-        </is>
-      </c>
-      <c r="R167" s="3" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
@@ -14924,51 +14609,131 @@
           <t>화면 로직</t>
         </is>
       </c>
-      <c r="L168" s="3" t="inlineStr">
-        <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="M168" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="L168" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
         </is>
       </c>
       <c r="N168" s="3" t="inlineStr">
         <is>
-          <t>Chromium 1440x900 · mobile 390x844 · tablet 768x1024</t>
-        </is>
-      </c>
-      <c r="O168" s="3" t="inlineStr">
-        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="P168" s="3" t="inlineStr"/>
+      <c r="O168" s="3" t="inlineStr"/>
+      <c r="P168" s="3" t="inlineStr">
+        <is>
+          <t>0건</t>
+        </is>
+      </c>
       <c r="Q168" s="3" t="inlineStr">
         <is>
-          <t>0건</t>
-        </is>
-      </c>
-      <c r="R168" s="3" t="inlineStr">
-        <is>
           <t>2순위</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>TC-Z03</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>3차</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>A-13</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>/api/demo/reset</t>
+        </is>
+      </c>
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G169" s="3" t="inlineStr">
+        <is>
+          <t>리셋 삭제 범위의 경계 — 자식 행이 달린 실계정 · @farmfi.test 로 시작만 하는 이메일 · 이메일 없는 계정 · 연속 2회</t>
+        </is>
+      </c>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>배포본 e81d8a05 · 검수용 임시 계정 3종(본인확인 2건·계좌 1건 포함)</t>
+        </is>
+      </c>
+      <c r="I169" s="3" t="inlineStr">
+        <is>
+          <t>1. 임시 계정 3종 생성  2. 리셋 2회 연속 호출  3. 유저·본인확인·계좌·시드 대조  4. 임시 계정 정리</t>
+        </is>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>실계정 3종과 본인확인 기록은 보존 · 계좌 등 시연 데이터는 삭제 · 시드 7건 재생성 · 2회차도 같은 결과</t>
+        </is>
+      </c>
+      <c r="K169" s="3" t="inlineStr">
+        <is>
+          <t>서버 로직</t>
+        </is>
+      </c>
+      <c r="L169" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>API 직접 호출 (프로덕션)</t>
+        </is>
+      </c>
+      <c r="N169" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="O169" s="3" t="inlineStr">
+        <is>
+          <t>REQ-008</t>
+        </is>
+      </c>
+      <c r="P169" s="3" t="inlineStr">
+        <is>
+          <t>실계정 3/3 · 본인확인 2/2 · 계좌 0건 · 시드 7/7 · 2회차 동일 · 지점 3곳 정상</t>
+        </is>
+      </c>
+      <c r="Q169" s="3" t="inlineStr">
+        <is>
+          <t>1순위</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:R132"/>
   <dataValidations count="4">
-    <dataValidation sqref="M2:M168" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L169" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,Blocked,N/A,미실행"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F168" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F169" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"정상,경계,예외"</formula1>
     </dataValidation>
-    <dataValidation sqref="R2:R168" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q2:Q169" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1순위,2순위,3순위"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K168" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K169" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"서버 로직,화면 로직,디자인"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14982,7 +14747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U10"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14997,12 +14762,12 @@
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="38" customWidth="1" min="14" max="14"/>
-    <col width="74" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="38" customWidth="1" min="13" max="13"/>
+    <col width="74" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
     <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
     <col width="11" customWidth="1" min="19" max="19"/>
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="11" customWidth="1" min="21" max="21"/>
@@ -15071,45 +14836,30 @@
       </c>
       <c r="M1" s="12" t="inlineStr">
         <is>
-          <t>발견자</t>
+          <t>시각 자료·증거</t>
         </is>
       </c>
       <c r="N1" s="12" t="inlineStr">
         <is>
-          <t>시각 자료·증거</t>
+          <t>해결 방향 · 실제 수정</t>
         </is>
       </c>
       <c r="O1" s="12" t="inlineStr">
         <is>
-          <t>해결 방향 · 실제 수정</t>
+          <t>진행 상태</t>
         </is>
       </c>
       <c r="P1" s="12" t="inlineStr">
         <is>
-          <t>담당자</t>
+          <t>검수 상태</t>
         </is>
       </c>
       <c r="Q1" s="12" t="inlineStr">
         <is>
-          <t>진행 상태</t>
+          <t>처리 일시</t>
         </is>
       </c>
       <c r="R1" s="12" t="inlineStr">
-        <is>
-          <t>검수자</t>
-        </is>
-      </c>
-      <c r="S1" s="12" t="inlineStr">
-        <is>
-          <t>검수 상태</t>
-        </is>
-      </c>
-      <c r="T1" s="12" t="inlineStr">
-        <is>
-          <t>처리 일시</t>
-        </is>
-      </c>
-      <c r="U1" s="12" t="inlineStr">
         <is>
           <t>검수 일시</t>
         </is>
@@ -15178,41 +14928,30 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>QA(자동화)</t>
+          <t>out/flows.json TC-D11 · HoldingIssuance eventId deposit:toss_QA-TXK-0001:mint / :0002:mint</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>out/flows.json TC-D11 · HoldingIssuance eventId deposit:toss_QA-TXK-0001:mint / :0002:mint</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
           <t>confirmBankDeposit이 account.status를 CANCELLED만 검사하고 PAID를 검사하지 않았다. 계좌가 이미 PAID이거나 신청이 DEPOSIT_CONFIRMED 이상이면 REVIEW로 보내 확정도 발행도 하지 않게 했다(ba8ba306). 재검증 TC-X17~X20 통과.</t>
         </is>
       </c>
+      <c r="O2" s="13" t="inlineStr">
+        <is>
+          <t>처리 완료</t>
+        </is>
+      </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="Q2" s="13" t="inlineStr">
-        <is>
-          <t>처리 완료</t>
+          <t>검수 전</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>검수 전</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr"/>
     </row>
     <row r="3" ht="88" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -15277,41 +15016,30 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>QA(자동화)</t>
+          <t>out/flows2.json TC-S01 응답 {"success":true,"tokenAmount":5}</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>out/flows2.json TC-S01 응답 {"success":true,"tokenAmount":5}</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
           <t>화면 어디에서도 부르지 않는 구(舊) 잔액 차감 경로였다. 라우트를 제거했다(7cd93b1a). settleInvestment가 쓰는 lib/subscription.ts는 정상 경로 안쪽이라 유지. 재검증 TC-X13 404 확인.</t>
         </is>
       </c>
+      <c r="O3" s="13" t="inlineStr">
+        <is>
+          <t>처리 완료</t>
+        </is>
+      </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="Q3" s="13" t="inlineStr">
-        <is>
-          <t>처리 완료</t>
+          <t>검수 전</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>검수 전</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="88" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -15376,41 +15104,30 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>QA(자동화)</t>
+          <t>out/flows.json TC-O02 (QA 임시 프로젝트로 재현, 검증 후 삭제)</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>out/flows.json TC-O02 (QA 임시 프로젝트로 재현, 검증 후 삭제)</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
           <t>가드가 `project.operatorId &amp;&amp; operatorId !== userId` 라서 null이면 통과했다. 판정을 ownsProject 한 곳으로 모으고 null도 거부하게 했다(85f89ea0). 재검증 TC-X14~X16 통과.</t>
         </is>
       </c>
+      <c r="O4" s="13" t="inlineStr">
+        <is>
+          <t>처리 완료</t>
+        </is>
+      </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="Q4" s="13" t="inlineStr">
-        <is>
-          <t>처리 완료</t>
+          <t>검수 전</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>검수 전</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr"/>
     </row>
     <row r="5" ht="88" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -15475,41 +15192,30 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>QA(자동화)</t>
+          <t>out/survey.json role=investor · 스크린샷 investor_admin.png</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>out/survey.json role=investor · 스크린샷 investor_admin.png</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
           <t>미들웨어 matcher가 /api/*와 구 리다이렉트 경로만 잡고 페이지에는 역할 가드가 없었다. /admin·/operator·/landlord·/monitoring·/optimization에 레이아웃 가드를 넣었다(24c962f2). 시연 계정 판정이 DB를 읽어야 해 미들웨어(edge)가 아니라 레이아웃에 뒀다. 재검증 TC-X07~X12 통과.</t>
         </is>
       </c>
+      <c r="O5" s="13" t="inlineStr">
+        <is>
+          <t>처리 완료</t>
+        </is>
+      </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="Q5" s="13" t="inlineStr">
-        <is>
-          <t>처리 완료</t>
+          <t>검수 전</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr">
-        <is>
-          <t>검수 전</t>
-        </is>
-      </c>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="88" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -15574,41 +15280,30 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>QA(자동화)</t>
+          <t>out/api-authz.json guest 행 · out/flows.json TC-A01·A02</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>out/api-authz.json guest 행 · out/flows.json TC-A01·A02</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
           <t>두 라우트에 monitoring과 같은 requireRole+guardProject를 붙였다(7441a2e7). QA 중 /optimization/[id] 화면이 서버 컴포넌트로 prisma를 직접 읽어 API 관문을 지나지 않는 것도 확인해 레이아웃 가드를 함께 넣었다. 재검증 TC-X01~X06 통과.</t>
         </is>
       </c>
+      <c r="O6" s="13" t="inlineStr">
+        <is>
+          <t>처리 완료</t>
+        </is>
+      </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="Q6" s="13" t="inlineStr">
-        <is>
-          <t>처리 완료</t>
+          <t>검수 전</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t>검수 전</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr"/>
     </row>
     <row r="7" ht="88" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -15673,41 +15368,30 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>QA(자동화)</t>
+          <t>out/shots/mobile_.png, mobile_projects.png, tablet_.png</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>out/shots/mobile_.png, mobile_projects.png, tablet_.png</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
           <t>1440 기준 값(좌우 54·간격 14·카드 3열·고정폭 검색창·히어로 음수 마진)이 폭에 상관없이 걸려 있었다. 헤더·셸·카드 그리드·지표 줄·단계 표시·주문 패널에 브레이크포인트를 넣었다(74909e57). 재검증 TC-X22·X23 통과.</t>
         </is>
       </c>
+      <c r="O7" s="13" t="inlineStr">
+        <is>
+          <t>처리 완료</t>
+        </is>
+      </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="Q7" s="13" t="inlineStr">
-        <is>
-          <t>처리 완료</t>
+          <t>검수 전</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr">
-        <is>
-          <t>검수 전</t>
-        </is>
-      </c>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr"/>
     </row>
     <row r="8" ht="88" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -15772,41 +15456,30 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>QA(자동화)</t>
+          <t>out/survey.json · MySubscriptionsScreen.tsx:166</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>out/survey.json · MySubscriptionsScreen.tsx:166</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
           <t>갈 곳이 없고 명세 B-07의 기능 목록에도 결제 내역이 없어 버튼을 제거했다(1f6038ea). /subscribe/payment는 신규 구독 draft에 의존해 기존 구독자를 보낼 수 없다. 재검증 TC-X21 통과.</t>
         </is>
       </c>
+      <c r="O8" s="13" t="inlineStr">
+        <is>
+          <t>처리 완료</t>
+        </is>
+      </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="Q8" s="13" t="inlineStr">
-        <is>
-          <t>처리 완료</t>
+          <t>검수 전</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t>검수 전</t>
-        </is>
-      </c>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr"/>
     </row>
     <row r="9" ht="88" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -15816,7 +15489,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>TC-Z02</t>
+          <t>TC-Z02, TC-Z03</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -15871,41 +15544,34 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>QA(자동화)</t>
+          <t>seed-scenario.ts:84 · 리셋 전후 User 테이블 조회 · 검수는 고칠 때와 다른 경우로 다시 봤다 — 자식 행이 달린 실계정 · @farmfi.test 로 시작만 하는 이메일 · 이메일 없는 계정 · 연속 리셋 2회 (TC-Z03, 7/7)</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>seed-scenario.ts:84 · 리셋 전후 User 테이블 조회 (실계정 소멸 → 수동 복원)</t>
+          <t>시드가 멱등하려면 지우고 다시 만드는 게 단순해서 유저 테이블을 통째로 비웠다. 시드가 만드는 계정은 전부 @farmfi.test 이므로 삭제 범위를 그 도메인으로 한정하고, 본인확인 기록은 남는 계정의 것만 남겼다(e81d8a05). 3차에서 리셋 후 실계정 1건과 본인확인 5건이 그대로 남는 것을 확인했다(TC-Z02).</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>시드가 멱등하려면 지우고 다시 만드는 게 단순해서 유저 테이블을 통째로 비웠다. 시드가 만드는 계정은 전부 @farmfi.test 이므로 삭제 범위를 그 도메인으로 한정하고, 본인확인 기록은 남는 계정의 것만 남겼다(e81d8a05). 3차에서 리셋 후 실계정 1건과 본인확인 5건이 그대로 남는 것을 확인했다(TC-Z02).</t>
+          <t>처리 완료</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>QA(자동화)</t>
+          <t>검수 완료</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>처리 완료</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr">
-        <is>
-          <t>검수 전</t>
-        </is>
-      </c>
-      <c r="T9" s="3" t="inlineStr">
-        <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="U9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="88" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -15970,41 +15636,30 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>QA(자동화)</t>
+          <t>리셋 응답 · User 테이블 조회 2회(없음) → 이후 조회(있음, 시드 순번 id cmt7kzoxr…) · 커밋 5ed2c88c 와 그 배포 시각</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>리셋 응답 · User 테이블 조회 2회(없음) → 이후 조회(있음, 시드 순번 id cmt7kzoxr…) · 커밋 5ed2c88c 와 그 배포 시각</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
           <t>결함이 아니다. 커밋 5ed2c88c `feat: 초기화해도 시연 계정이 살아남게 한다`(08-24 22:07)가 시드에 시연 계정 생성 블록을 넣었고, 그 배포가 내 관측 두 번 사이에 들어갔다. 앞선 두 번은 그 블록이 없는 배포본이었다. 남기는 이유는 하나다 — QA 중에 다른 세션이 같은 저장소에 배포하면 같은 TC 가 다른 코드를 본다. 라운드마다 배포 커밋 SHA 를 적는다.</t>
         </is>
       </c>
+      <c r="O10" s="13" t="inlineStr">
+        <is>
+          <t>처리 완료</t>
+        </is>
+      </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>QA(자동화)</t>
-        </is>
-      </c>
-      <c r="Q10" s="13" t="inlineStr">
-        <is>
-          <t>처리 완료</t>
+          <t>검수 전</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr">
-        <is>
-          <t>검수 전</t>
-        </is>
-      </c>
-      <c r="T10" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:U10"/>
@@ -16021,10 +15676,10 @@
     <dataValidation sqref="K2:K10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"항상,가끔,1회"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"확인 전,처리 중,처리 완료,검수 완료,보류"</formula1>
     </dataValidation>
-    <dataValidation sqref="S2:S10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"검수 전,검수 완료,반려"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16038,7 +15693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -16046,8 +15701,9 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16078,16 +15734,6 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>담당 A</t>
-        </is>
-      </c>
-      <c r="G1" s="12" t="inlineStr">
-        <is>
-          <t>담당 B</t>
-        </is>
-      </c>
-      <c r="H1" s="12" t="inlineStr">
-        <is>
           <t>비고</t>
         </is>
       </c>
@@ -16116,9 +15762,7 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>투자자 세션으로 /admin·/operator 화면이 200 렌더 → 레이아웃 가드 후 자기 역할 홈으로 리다이렉트</t>
         </is>
@@ -16148,9 +15792,7 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>31개 중 /api/projects 는 명세 2장에서 비회원 공개. 나머지 30개 중 28개 정상 401, optimization·briefing 2개가 200이었다</t>
         </is>
@@ -16180,9 +15822,7 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>54/58 무오류. 나머지 4건은 투자자 세션의 권한 밖 화면 — 3건은 API 403(정상 방어), 1건은 /subscriptions 의 404 → REQ-007</t>
         </is>
@@ -16212,9 +15852,7 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>홈 1010px · 프로젝트 568px · 정기구독 546px · 소개 627px → 전부 뷰포트 이내</t>
         </is>
@@ -16244,9 +15882,7 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>1차 검출 0건. 요청 3으로 '총 배정 토큰·내 보유 토큰' 라벨이 들어가, 3차에서 그 둘을 명세 18장 예외로 두고 다시 검사했다 — 0건</t>
         </is>
@@ -16276,9 +15912,7 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>명세 14장 오류 코드 문구 — 400/403 응답 모두 한국어 사유 포함</t>
         </is>
@@ -16308,9 +15942,7 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>/api/demo/reset 으로 모집액·발행·입금 기록 원복 확인. 3차부터는 리셋이 시드 계정만 지우므로 실계정과 본인확인 기록을 백업할 필요가 없다(REQ-008).</t>
         </is>
